--- a/outputs/pd_css_cross/Segments3_report.xlsx
+++ b/outputs/pd_css_cross/Segments3_report.xlsx
@@ -257,43 +257,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.5211267605633803</c:v>
+                  <c:v>0.8131868131868132</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5189873417721519</c:v>
+                  <c:v>0.9047619047619048</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6410256410256411</c:v>
+                  <c:v>0.9047619047619048</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5689655172413793</c:v>
+                  <c:v>0.937888198757764</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6949152542372882</c:v>
+                  <c:v>0.9182389937106918</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7083333333333334</c:v>
+                  <c:v>0.9047619047619048</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6341463414634146</c:v>
+                  <c:v>0.8873239436619719</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6571428571428571</c:v>
+                  <c:v>0.8686131386861314</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3928571428571428</c:v>
+                  <c:v>0.8625954198473282</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.6363636363636364</c:v>
+                  <c:v>0.881578947368421</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5384615384615384</c:v>
+                  <c:v>0.8095238095238095</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5526315789473685</c:v>
+                  <c:v>0.8222222222222222</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6216216216216216</c:v>
+                  <c:v>0.8706896551724138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -371,43 +371,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1891891891891892</c:v>
+                  <c:v>0.3269230769230769</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25</c:v>
+                  <c:v>0.4864864864864865</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2166666666666667</c:v>
+                  <c:v>0.4943181818181818</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2857142857142857</c:v>
+                  <c:v>0.4539473684210527</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2352941176470588</c:v>
+                  <c:v>0.5135135135135135</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1551724137931035</c:v>
+                  <c:v>0.4802631578947368</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964285714285714</c:v>
+                  <c:v>0.4901960784313725</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2765957446808511</c:v>
+                  <c:v>0.4796747967479675</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2549019607843137</c:v>
+                  <c:v>0.456</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2916666666666667</c:v>
+                  <c:v>0.5528455284552846</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.375</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3333333333333333</c:v>
+                  <c:v>0.5597014925373134</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2380952380952381</c:v>
+                  <c:v>0.5357142857142857</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -485,43 +485,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.07692307692307693</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.08333333333333333</c:v>
+                  <c:v>0.07954545454545454</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1739130434782609</c:v>
+                  <c:v>0.09174311926605505</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2</c:v>
+                  <c:v>0.1458333333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1282051282051282</c:v>
+                  <c:v>0.1052631578947368</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1627906976744186</c:v>
+                  <c:v>0.1395348837209302</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.16</c:v>
+                  <c:v>0.1458333333333333</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.09836065573770492</c:v>
+                  <c:v>0.1059602649006623</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1857142857142857</c:v>
+                  <c:v>0.09580838323353294</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.180327868852459</c:v>
+                  <c:v>0.09659090909090909</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.07792207792207792</c:v>
+                  <c:v>0.1047120418848168</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1267605633802817</c:v>
+                  <c:v>0.1170212765957447</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.07894736842105263</c:v>
+                  <c:v>0.07804878048780488</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -699,43 +699,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.5867768595041323</c:v>
+                  <c:v>0.4619289340101523</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6030534351145038</c:v>
+                  <c:v>0.3809523809523809</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.484472049689441</c:v>
+                  <c:v>0.3402777777777778</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3558282208588957</c:v>
+                  <c:v>0.3522975929978118</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3959731543624161</c:v>
+                  <c:v>0.3613636363636364</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3221476510067114</c:v>
+                  <c:v>0.3095823095823096</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2789115646258503</c:v>
+                  <c:v>0.3234624145785877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2447552447552448</c:v>
+                  <c:v>0.3333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1879194630872483</c:v>
+                  <c:v>0.3096926713947991</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2323943661971831</c:v>
+                  <c:v>0.3370288248337029</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1925925925925926</c:v>
+                  <c:v>0.2923433874709977</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2567567567567567</c:v>
+                  <c:v>0.2954048140043763</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2387096774193548</c:v>
+                  <c:v>0.2516268980477224</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -813,43 +813,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3057851239669421</c:v>
+                  <c:v>0.3959390862944163</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3053435114503817</c:v>
+                  <c:v>0.4195011337868481</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3726708074534161</c:v>
+                  <c:v>0.4074074074074074</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4294478527607362</c:v>
+                  <c:v>0.3326039387308534</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3422818791946309</c:v>
+                  <c:v>0.3363636363636364</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3892617449664429</c:v>
+                  <c:v>0.3734643734643734</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3809523809523809</c:v>
+                  <c:v>0.3485193621867881</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3286713286713286</c:v>
+                  <c:v>0.2992700729927008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3422818791946309</c:v>
+                  <c:v>0.2955082742316785</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3380281690140845</c:v>
+                  <c:v>0.2727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.237037037037037</c:v>
+                  <c:v>0.2645011600928074</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2635135135135135</c:v>
+                  <c:v>0.2932166301969366</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2709677419354839</c:v>
+                  <c:v>0.3036876355748373</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -927,43 +927,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1074380165289256</c:v>
+                  <c:v>0.1421319796954315</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0916030534351145</c:v>
+                  <c:v>0.199546485260771</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1428571428571428</c:v>
+                  <c:v>0.2523148148148148</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2147239263803681</c:v>
+                  <c:v>0.3150984682713348</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.261744966442953</c:v>
+                  <c:v>0.3022727272727272</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2885906040268457</c:v>
+                  <c:v>0.316953316953317</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3401360544217687</c:v>
+                  <c:v>0.3280182232346242</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4265734265734266</c:v>
+                  <c:v>0.3673965936739659</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4697986577181208</c:v>
+                  <c:v>0.3947990543735225</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.4295774647887324</c:v>
+                  <c:v>0.3902439024390244</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5703703703703704</c:v>
+                  <c:v>0.4431554524361949</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4797297297297297</c:v>
+                  <c:v>0.4113785557986871</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4903225806451613</c:v>
+                  <c:v>0.4446854663774403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1141,43 +1141,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.5211267605633803</c:v>
+                  <c:v>0.8131868131868132</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5189873417721519</c:v>
+                  <c:v>0.9047619047619048</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6410256410256411</c:v>
+                  <c:v>0.9047619047619048</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5689655172413793</c:v>
+                  <c:v>0.937888198757764</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6949152542372882</c:v>
+                  <c:v>0.9182389937106918</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7083333333333334</c:v>
+                  <c:v>0.9047619047619048</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6341463414634146</c:v>
+                  <c:v>0.8873239436619719</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6571428571428571</c:v>
+                  <c:v>0.8686131386861314</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3928571428571428</c:v>
+                  <c:v>0.8625954198473282</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.6363636363636364</c:v>
+                  <c:v>0.881578947368421</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5384615384615384</c:v>
+                  <c:v>0.8095238095238095</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5526315789473685</c:v>
+                  <c:v>0.8222222222222222</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6216216216216216</c:v>
+                  <c:v>0.8706896551724138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1255,43 +1255,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1891891891891892</c:v>
+                  <c:v>0.3269230769230769</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25</c:v>
+                  <c:v>0.4864864864864865</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2166666666666667</c:v>
+                  <c:v>0.4943181818181818</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2857142857142857</c:v>
+                  <c:v>0.4539473684210527</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2352941176470588</c:v>
+                  <c:v>0.5135135135135135</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1551724137931035</c:v>
+                  <c:v>0.4802631578947368</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964285714285714</c:v>
+                  <c:v>0.4901960784313725</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2765957446808511</c:v>
+                  <c:v>0.4796747967479675</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2549019607843137</c:v>
+                  <c:v>0.456</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2916666666666667</c:v>
+                  <c:v>0.5528455284552846</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.375</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3333333333333333</c:v>
+                  <c:v>0.5597014925373134</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2380952380952381</c:v>
+                  <c:v>0.5357142857142857</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1369,43 +1369,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.07692307692307693</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.08333333333333333</c:v>
+                  <c:v>0.07954545454545454</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1739130434782609</c:v>
+                  <c:v>0.09174311926605505</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2</c:v>
+                  <c:v>0.1458333333333333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1282051282051282</c:v>
+                  <c:v>0.1052631578947368</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1627906976744186</c:v>
+                  <c:v>0.1395348837209302</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.16</c:v>
+                  <c:v>0.1458333333333333</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.09836065573770492</c:v>
+                  <c:v>0.1059602649006623</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1857142857142857</c:v>
+                  <c:v>0.09580838323353294</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.180327868852459</c:v>
+                  <c:v>0.09659090909090909</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.07792207792207792</c:v>
+                  <c:v>0.1047120418848168</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1267605633802817</c:v>
+                  <c:v>0.1170212765957447</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.07894736842105263</c:v>
+                  <c:v>0.07804878048780488</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1583,43 +1583,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.5867768595041323</c:v>
+                  <c:v>0.4619289340101523</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6030534351145038</c:v>
+                  <c:v>0.3809523809523809</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.484472049689441</c:v>
+                  <c:v>0.3402777777777778</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3558282208588957</c:v>
+                  <c:v>0.3522975929978118</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3959731543624161</c:v>
+                  <c:v>0.3613636363636364</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3221476510067114</c:v>
+                  <c:v>0.3095823095823096</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2789115646258503</c:v>
+                  <c:v>0.3234624145785877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2447552447552448</c:v>
+                  <c:v>0.3333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1879194630872483</c:v>
+                  <c:v>0.3096926713947991</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2323943661971831</c:v>
+                  <c:v>0.3370288248337029</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1925925925925926</c:v>
+                  <c:v>0.2923433874709977</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2567567567567567</c:v>
+                  <c:v>0.2954048140043763</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2387096774193548</c:v>
+                  <c:v>0.2516268980477224</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1697,43 +1697,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3057851239669421</c:v>
+                  <c:v>0.3959390862944163</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3053435114503817</c:v>
+                  <c:v>0.4195011337868481</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3726708074534161</c:v>
+                  <c:v>0.4074074074074074</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4294478527607362</c:v>
+                  <c:v>0.3326039387308534</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3422818791946309</c:v>
+                  <c:v>0.3363636363636364</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3892617449664429</c:v>
+                  <c:v>0.3734643734643734</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3809523809523809</c:v>
+                  <c:v>0.3485193621867881</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3286713286713286</c:v>
+                  <c:v>0.2992700729927008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3422818791946309</c:v>
+                  <c:v>0.2955082742316785</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3380281690140845</c:v>
+                  <c:v>0.2727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.237037037037037</c:v>
+                  <c:v>0.2645011600928074</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2635135135135135</c:v>
+                  <c:v>0.2932166301969366</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2709677419354839</c:v>
+                  <c:v>0.3036876355748373</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,43 +1811,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1074380165289256</c:v>
+                  <c:v>0.1421319796954315</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0916030534351145</c:v>
+                  <c:v>0.199546485260771</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1428571428571428</c:v>
+                  <c:v>0.2523148148148148</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2147239263803681</c:v>
+                  <c:v>0.3150984682713348</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.261744966442953</c:v>
+                  <c:v>0.3022727272727272</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2885906040268457</c:v>
+                  <c:v>0.316953316953317</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3401360544217687</c:v>
+                  <c:v>0.3280182232346242</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4265734265734266</c:v>
+                  <c:v>0.3673965936739659</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4697986577181208</c:v>
+                  <c:v>0.3947990543735225</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.4295774647887324</c:v>
+                  <c:v>0.3902439024390244</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5703703703703704</c:v>
+                  <c:v>0.4431554524361949</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4797297297297297</c:v>
+                  <c:v>0.4113785557986871</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4903225806451613</c:v>
+                  <c:v>0.4446854663774403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1938,7 +1938,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
+      <xdr:colOff>1028700</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1968,7 +1968,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
+      <xdr:colOff>1028700</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -2003,7 +2003,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
+      <xdr:colOff>1028700</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -2033,7 +2033,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
+      <xdr:colOff>1028700</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -2346,7 +2346,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="21.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
     <col min="6" max="7" width="10.7109375" style="3" customWidth="1"/>
@@ -2402,22 +2403,22 @@
         <v>0</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.5174374683146535</v>
+        <v>0.9502345014917034</v>
       </c>
       <c r="C4" s="1">
-        <v>3.203767666961591</v>
+        <v>8.014037340297495</v>
       </c>
       <c r="D4" s="2">
-        <v>0.5942947702060222</v>
+        <v>0.8767268862911796</v>
       </c>
       <c r="E4" s="2">
-        <v>0.3333333333333333</v>
+        <v>0.3334514528703048</v>
       </c>
       <c r="F4" s="3">
-        <v>631</v>
+        <v>1882</v>
       </c>
       <c r="G4" s="3">
-        <v>375</v>
+        <v>1650</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
@@ -2426,16 +2427,16 @@
         <v>8</v>
       </c>
       <c r="K4" s="2">
-        <v>0.5211267605633803</v>
+        <v>0.8131868131868132</v>
       </c>
       <c r="L4" s="2">
-        <v>0.5867768595041323</v>
+        <v>0.4619289340101523</v>
       </c>
       <c r="M4" s="3">
-        <v>71</v>
+        <v>182</v>
       </c>
       <c r="N4" s="3">
-        <v>37</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2443,22 +2444,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>-1.135530545938961</v>
+        <v>-1.043918035281563</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.5181460438793203</v>
+        <v>0.9500194933372372</v>
       </c>
       <c r="D5" s="2">
-        <v>0.248811410459588</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="E5" s="2">
-        <v>0.3333333333333333</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F5" s="3">
-        <v>631</v>
+        <v>1881</v>
       </c>
       <c r="G5" s="3">
-        <v>157</v>
+        <v>912</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -2467,16 +2468,16 @@
         <v>9</v>
       </c>
       <c r="K5" s="2">
-        <v>0.5189873417721519</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L5" s="2">
-        <v>0.6030534351145038</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M5" s="3">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="N5" s="3">
-        <v>41</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2484,22 +2485,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>-2.435104178233598</v>
+        <v>-10.8317280747611</v>
       </c>
       <c r="C6" s="1">
-        <v>-1.136348485150166</v>
+        <v>-1.045108577584102</v>
       </c>
       <c r="D6" s="2">
-        <v>0.133122028526149</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="E6" s="2">
-        <v>0.3333333333333333</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F6" s="3">
-        <v>631</v>
+        <v>1881</v>
       </c>
       <c r="G6" s="3">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -2508,16 +2509,16 @@
         <v>10</v>
       </c>
       <c r="K6" s="2">
-        <v>0.6410256410256411</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L6" s="2">
-        <v>0.484472049689441</v>
+        <v>0.3402777777777778</v>
       </c>
       <c r="M6" s="3">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="N6" s="3">
-        <v>50</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2528,16 +2529,16 @@
         <v>11</v>
       </c>
       <c r="K7" s="2">
-        <v>0.5689655172413793</v>
+        <v>0.937888198757764</v>
       </c>
       <c r="L7" s="2">
-        <v>0.3558282208588957</v>
+        <v>0.3522975929978118</v>
       </c>
       <c r="M7" s="3">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="N7" s="3">
-        <v>33</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2548,16 +2549,16 @@
         <v>12</v>
       </c>
       <c r="K8" s="2">
-        <v>0.6949152542372882</v>
+        <v>0.9182389937106918</v>
       </c>
       <c r="L8" s="2">
-        <v>0.3959731543624161</v>
+        <v>0.3613636363636364</v>
       </c>
       <c r="M8" s="3">
-        <v>59</v>
+        <v>159</v>
       </c>
       <c r="N8" s="3">
-        <v>41</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2568,16 +2569,16 @@
         <v>13</v>
       </c>
       <c r="K9" s="2">
-        <v>0.7083333333333334</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L9" s="2">
-        <v>0.3221476510067114</v>
+        <v>0.3095823095823096</v>
       </c>
       <c r="M9" s="3">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="N9" s="3">
-        <v>34</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2588,16 +2589,16 @@
         <v>14</v>
       </c>
       <c r="K10" s="2">
-        <v>0.6341463414634146</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="L10" s="2">
-        <v>0.2789115646258503</v>
+        <v>0.3234624145785877</v>
       </c>
       <c r="M10" s="3">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="N10" s="3">
-        <v>26</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2608,16 +2609,16 @@
         <v>15</v>
       </c>
       <c r="K11" s="2">
-        <v>0.6571428571428571</v>
+        <v>0.8686131386861314</v>
       </c>
       <c r="L11" s="2">
-        <v>0.2447552447552448</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M11" s="3">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="N11" s="3">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2628,16 +2629,16 @@
         <v>16</v>
       </c>
       <c r="K12" s="2">
-        <v>0.3928571428571428</v>
+        <v>0.8625954198473282</v>
       </c>
       <c r="L12" s="2">
-        <v>0.1879194630872483</v>
+        <v>0.3096926713947991</v>
       </c>
       <c r="M12" s="3">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="N12" s="3">
-        <v>11</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2648,16 +2649,16 @@
         <v>17</v>
       </c>
       <c r="K13" s="2">
-        <v>0.6363636363636364</v>
+        <v>0.881578947368421</v>
       </c>
       <c r="L13" s="2">
-        <v>0.2323943661971831</v>
+        <v>0.3370288248337029</v>
       </c>
       <c r="M13" s="3">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="N13" s="3">
-        <v>21</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -2668,16 +2669,16 @@
         <v>18</v>
       </c>
       <c r="K14" s="2">
-        <v>0.5384615384615384</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L14" s="2">
-        <v>0.1925925925925926</v>
+        <v>0.2923433874709977</v>
       </c>
       <c r="M14" s="3">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="N14" s="3">
-        <v>14</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2688,16 +2689,16 @@
         <v>19</v>
       </c>
       <c r="K15" s="2">
-        <v>0.5526315789473685</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="L15" s="2">
-        <v>0.2567567567567567</v>
+        <v>0.2954048140043763</v>
       </c>
       <c r="M15" s="3">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="N15" s="3">
-        <v>21</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2708,16 +2709,16 @@
         <v>20</v>
       </c>
       <c r="K16" s="2">
-        <v>0.6216216216216216</v>
+        <v>0.8706896551724138</v>
       </c>
       <c r="L16" s="2">
-        <v>0.2387096774193548</v>
+        <v>0.2516268980477224</v>
       </c>
       <c r="M16" s="3">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="N16" s="3">
-        <v>23</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="9:14">
@@ -2728,16 +2729,16 @@
         <v>8</v>
       </c>
       <c r="K17" s="2">
-        <v>0.1891891891891892</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="L17" s="2">
-        <v>0.3057851239669421</v>
+        <v>0.3959390862944163</v>
       </c>
       <c r="M17" s="3">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="N17" s="3">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="9:14">
@@ -2748,16 +2749,16 @@
         <v>9</v>
       </c>
       <c r="K18" s="2">
-        <v>0.25</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="L18" s="2">
-        <v>0.3053435114503817</v>
+        <v>0.4195011337868481</v>
       </c>
       <c r="M18" s="3">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="N18" s="3">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="9:14">
@@ -2768,16 +2769,16 @@
         <v>10</v>
       </c>
       <c r="K19" s="2">
-        <v>0.2166666666666667</v>
+        <v>0.4943181818181818</v>
       </c>
       <c r="L19" s="2">
-        <v>0.3726708074534161</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="M19" s="3">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="N19" s="3">
-        <v>13</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="9:14">
@@ -2788,16 +2789,16 @@
         <v>11</v>
       </c>
       <c r="K20" s="2">
-        <v>0.2857142857142857</v>
+        <v>0.4539473684210527</v>
       </c>
       <c r="L20" s="2">
-        <v>0.4294478527607362</v>
+        <v>0.3326039387308534</v>
       </c>
       <c r="M20" s="3">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="N20" s="3">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="9:14">
@@ -2808,16 +2809,16 @@
         <v>12</v>
       </c>
       <c r="K21" s="2">
-        <v>0.2352941176470588</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="L21" s="2">
-        <v>0.3422818791946309</v>
+        <v>0.3363636363636364</v>
       </c>
       <c r="M21" s="3">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="N21" s="3">
-        <v>12</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="9:14">
@@ -2828,16 +2829,16 @@
         <v>13</v>
       </c>
       <c r="K22" s="2">
-        <v>0.1551724137931035</v>
+        <v>0.4802631578947368</v>
       </c>
       <c r="L22" s="2">
-        <v>0.3892617449664429</v>
+        <v>0.3734643734643734</v>
       </c>
       <c r="M22" s="3">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="N22" s="3">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="9:14">
@@ -2848,16 +2849,16 @@
         <v>14</v>
       </c>
       <c r="K23" s="2">
-        <v>0.1964285714285714</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="L23" s="2">
-        <v>0.3809523809523809</v>
+        <v>0.3485193621867881</v>
       </c>
       <c r="M23" s="3">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="N23" s="3">
-        <v>11</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="9:14">
@@ -2868,16 +2869,16 @@
         <v>15</v>
       </c>
       <c r="K24" s="2">
-        <v>0.2765957446808511</v>
+        <v>0.4796747967479675</v>
       </c>
       <c r="L24" s="2">
-        <v>0.3286713286713286</v>
+        <v>0.2992700729927008</v>
       </c>
       <c r="M24" s="3">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="N24" s="3">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="9:14">
@@ -2888,16 +2889,16 @@
         <v>16</v>
       </c>
       <c r="K25" s="2">
-        <v>0.2549019607843137</v>
+        <v>0.456</v>
       </c>
       <c r="L25" s="2">
-        <v>0.3422818791946309</v>
+        <v>0.2955082742316785</v>
       </c>
       <c r="M25" s="3">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="N25" s="3">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="9:14">
@@ -2908,16 +2909,16 @@
         <v>17</v>
       </c>
       <c r="K26" s="2">
-        <v>0.2916666666666667</v>
+        <v>0.5528455284552846</v>
       </c>
       <c r="L26" s="2">
-        <v>0.3380281690140845</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="M26" s="3">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="N26" s="3">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="9:14">
@@ -2928,16 +2929,16 @@
         <v>18</v>
       </c>
       <c r="K27" s="2">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="2">
-        <v>0.237037037037037</v>
+        <v>0.2645011600928074</v>
       </c>
       <c r="M27" s="3">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="N27" s="3">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="9:14">
@@ -2948,16 +2949,16 @@
         <v>19</v>
       </c>
       <c r="K28" s="2">
-        <v>0.3333333333333333</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="L28" s="2">
-        <v>0.2635135135135135</v>
+        <v>0.2932166301969366</v>
       </c>
       <c r="M28" s="3">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="N28" s="3">
-        <v>13</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="9:14">
@@ -2968,16 +2969,16 @@
         <v>20</v>
       </c>
       <c r="K29" s="2">
-        <v>0.2380952380952381</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="L29" s="2">
-        <v>0.2709677419354839</v>
+        <v>0.3036876355748373</v>
       </c>
       <c r="M29" s="3">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="N29" s="3">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="9:14">
@@ -2988,16 +2989,16 @@
         <v>8</v>
       </c>
       <c r="K30" s="2">
-        <v>0.07692307692307693</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2">
-        <v>0.1074380165289256</v>
+        <v>0.1421319796954315</v>
       </c>
       <c r="M30" s="3">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="N30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="9:14">
@@ -3008,16 +3009,16 @@
         <v>9</v>
       </c>
       <c r="K31" s="2">
-        <v>0.08333333333333333</v>
+        <v>0.07954545454545454</v>
       </c>
       <c r="L31" s="2">
-        <v>0.0916030534351145</v>
+        <v>0.199546485260771</v>
       </c>
       <c r="M31" s="3">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="N31" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="9:14">
@@ -3028,16 +3029,16 @@
         <v>10</v>
       </c>
       <c r="K32" s="2">
-        <v>0.1739130434782609</v>
+        <v>0.09174311926605505</v>
       </c>
       <c r="L32" s="2">
-        <v>0.1428571428571428</v>
+        <v>0.2523148148148148</v>
       </c>
       <c r="M32" s="3">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="N32" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="9:14">
@@ -3048,16 +3049,16 @@
         <v>11</v>
       </c>
       <c r="K33" s="2">
-        <v>0.2</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="L33" s="2">
-        <v>0.2147239263803681</v>
+        <v>0.3150984682713348</v>
       </c>
       <c r="M33" s="3">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="N33" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="9:14">
@@ -3068,16 +3069,16 @@
         <v>12</v>
       </c>
       <c r="K34" s="2">
-        <v>0.1282051282051282</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="L34" s="2">
-        <v>0.261744966442953</v>
+        <v>0.3022727272727272</v>
       </c>
       <c r="M34" s="3">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="N34" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="9:14">
@@ -3088,16 +3089,16 @@
         <v>13</v>
       </c>
       <c r="K35" s="2">
-        <v>0.1627906976744186</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="L35" s="2">
-        <v>0.2885906040268457</v>
+        <v>0.316953316953317</v>
       </c>
       <c r="M35" s="3">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="N35" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="9:14">
@@ -3108,16 +3109,16 @@
         <v>14</v>
       </c>
       <c r="K36" s="2">
-        <v>0.16</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="L36" s="2">
-        <v>0.3401360544217687</v>
+        <v>0.3280182232346242</v>
       </c>
       <c r="M36" s="3">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="N36" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="9:14">
@@ -3128,16 +3129,16 @@
         <v>15</v>
       </c>
       <c r="K37" s="2">
-        <v>0.09836065573770492</v>
+        <v>0.1059602649006623</v>
       </c>
       <c r="L37" s="2">
-        <v>0.4265734265734266</v>
+        <v>0.3673965936739659</v>
       </c>
       <c r="M37" s="3">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="N37" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="9:14">
@@ -3148,16 +3149,16 @@
         <v>16</v>
       </c>
       <c r="K38" s="2">
-        <v>0.1857142857142857</v>
+        <v>0.09580838323353294</v>
       </c>
       <c r="L38" s="2">
-        <v>0.4697986577181208</v>
+        <v>0.3947990543735225</v>
       </c>
       <c r="M38" s="3">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="N38" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="9:14">
@@ -3168,16 +3169,16 @@
         <v>17</v>
       </c>
       <c r="K39" s="2">
-        <v>0.180327868852459</v>
+        <v>0.09659090909090909</v>
       </c>
       <c r="L39" s="2">
-        <v>0.4295774647887324</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="M39" s="3">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="N39" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="9:14">
@@ -3188,16 +3189,16 @@
         <v>18</v>
       </c>
       <c r="K40" s="2">
-        <v>0.07792207792207792</v>
+        <v>0.1047120418848168</v>
       </c>
       <c r="L40" s="2">
-        <v>0.5703703703703704</v>
+        <v>0.4431554524361949</v>
       </c>
       <c r="M40" s="3">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="N40" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="9:14">
@@ -3208,16 +3209,16 @@
         <v>19</v>
       </c>
       <c r="K41" s="2">
-        <v>0.1267605633802817</v>
+        <v>0.1170212765957447</v>
       </c>
       <c r="L41" s="2">
-        <v>0.4797297297297297</v>
+        <v>0.4113785557986871</v>
       </c>
       <c r="M41" s="3">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="N41" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="9:14">
@@ -3228,16 +3229,16 @@
         <v>20</v>
       </c>
       <c r="K42" s="2">
-        <v>0.07894736842105263</v>
+        <v>0.07804878048780488</v>
       </c>
       <c r="L42" s="2">
-        <v>0.4903225806451613</v>
+        <v>0.4446854663774403</v>
       </c>
       <c r="M42" s="3">
-        <v>76</v>
+        <v>205</v>
       </c>
       <c r="N42" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3253,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="21.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" style="1" customWidth="1"/>
@@ -3311,22 +3313,22 @@
         <v>0</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.5174374683146535</v>
+        <v>0.9502345014917034</v>
       </c>
       <c r="C4" s="1">
-        <v>3.203767666961591</v>
+        <v>8.014037340297495</v>
       </c>
       <c r="D4" s="2">
-        <v>0.5942947702060222</v>
+        <v>0.8767268862911796</v>
       </c>
       <c r="E4" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.3334514528703048</v>
       </c>
       <c r="F4" s="1">
-        <v>3155000</v>
+        <v>9410000</v>
       </c>
       <c r="G4" s="1">
-        <v>1875000</v>
+        <v>8250000</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
@@ -3335,16 +3337,16 @@
         <v>8</v>
       </c>
       <c r="K4" s="2">
-        <v>0.5211267605633803</v>
+        <v>0.8131868131868132</v>
       </c>
       <c r="L4" s="1">
-        <v>0.5867768595041323</v>
+        <v>0.4619289340101523</v>
       </c>
       <c r="M4" s="1">
-        <v>355000</v>
+        <v>910000</v>
       </c>
       <c r="N4" s="1">
-        <v>185000</v>
+        <v>740000</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3352,22 +3354,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>-1.135530545938961</v>
+        <v>-1.043918035281563</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.5181460438793203</v>
+        <v>0.9500194933372372</v>
       </c>
       <c r="D5" s="2">
-        <v>0.248811410459588</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="E5" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F5" s="1">
-        <v>3155000</v>
+        <v>9405000</v>
       </c>
       <c r="G5" s="1">
-        <v>785000</v>
+        <v>4560000</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -3376,16 +3378,16 @@
         <v>9</v>
       </c>
       <c r="K5" s="2">
-        <v>0.5189873417721519</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L5" s="1">
-        <v>0.6030534351145038</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="M5" s="1">
-        <v>395000</v>
+        <v>840000</v>
       </c>
       <c r="N5" s="1">
-        <v>205000</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3393,22 +3395,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>-2.435104178233598</v>
+        <v>-10.8317280747611</v>
       </c>
       <c r="C6" s="1">
-        <v>-1.136348485150166</v>
+        <v>-1.045108577584102</v>
       </c>
       <c r="D6" s="2">
-        <v>0.133122028526149</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="E6" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F6" s="1">
-        <v>3155000</v>
+        <v>9405000</v>
       </c>
       <c r="G6" s="1">
-        <v>420000</v>
+        <v>990000</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -3417,16 +3419,16 @@
         <v>10</v>
       </c>
       <c r="K6" s="2">
-        <v>0.6410256410256411</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L6" s="1">
-        <v>0.484472049689441</v>
+        <v>0.3402777777777778</v>
       </c>
       <c r="M6" s="1">
-        <v>390000</v>
+        <v>735000</v>
       </c>
       <c r="N6" s="1">
-        <v>250000</v>
+        <v>665000</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3437,16 +3439,16 @@
         <v>11</v>
       </c>
       <c r="K7" s="2">
-        <v>0.5689655172413793</v>
+        <v>0.937888198757764</v>
       </c>
       <c r="L7" s="1">
-        <v>0.3558282208588957</v>
+        <v>0.3522975929978118</v>
       </c>
       <c r="M7" s="1">
-        <v>290000</v>
+        <v>805000</v>
       </c>
       <c r="N7" s="1">
-        <v>165000</v>
+        <v>755000</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3457,16 +3459,16 @@
         <v>12</v>
       </c>
       <c r="K8" s="2">
-        <v>0.6949152542372882</v>
+        <v>0.9182389937106918</v>
       </c>
       <c r="L8" s="1">
-        <v>0.3959731543624161</v>
+        <v>0.3613636363636364</v>
       </c>
       <c r="M8" s="1">
-        <v>295000</v>
+        <v>795000</v>
       </c>
       <c r="N8" s="1">
-        <v>205000</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -3477,16 +3479,16 @@
         <v>13</v>
       </c>
       <c r="K9" s="2">
-        <v>0.7083333333333334</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L9" s="1">
-        <v>0.3221476510067114</v>
+        <v>0.3095823095823096</v>
       </c>
       <c r="M9" s="1">
-        <v>240000</v>
+        <v>630000</v>
       </c>
       <c r="N9" s="1">
-        <v>170000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -3497,16 +3499,16 @@
         <v>14</v>
       </c>
       <c r="K10" s="2">
-        <v>0.6341463414634146</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="L10" s="1">
-        <v>0.2789115646258503</v>
+        <v>0.3234624145785877</v>
       </c>
       <c r="M10" s="1">
-        <v>205000</v>
+        <v>710000</v>
       </c>
       <c r="N10" s="1">
-        <v>130000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -3517,16 +3519,16 @@
         <v>15</v>
       </c>
       <c r="K11" s="2">
-        <v>0.6571428571428571</v>
+        <v>0.8686131386861314</v>
       </c>
       <c r="L11" s="1">
-        <v>0.2447552447552448</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M11" s="1">
-        <v>175000</v>
+        <v>685000</v>
       </c>
       <c r="N11" s="1">
-        <v>115000</v>
+        <v>595000</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3537,16 +3539,16 @@
         <v>16</v>
       </c>
       <c r="K12" s="2">
-        <v>0.3928571428571428</v>
+        <v>0.8625954198473282</v>
       </c>
       <c r="L12" s="1">
-        <v>0.1879194630872483</v>
+        <v>0.3096926713947991</v>
       </c>
       <c r="M12" s="1">
-        <v>140000</v>
+        <v>655000</v>
       </c>
       <c r="N12" s="1">
-        <v>55000</v>
+        <v>565000</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3557,16 +3559,16 @@
         <v>17</v>
       </c>
       <c r="K13" s="2">
-        <v>0.6363636363636364</v>
+        <v>0.881578947368421</v>
       </c>
       <c r="L13" s="1">
-        <v>0.2323943661971831</v>
+        <v>0.3370288248337029</v>
       </c>
       <c r="M13" s="1">
-        <v>165000</v>
+        <v>760000</v>
       </c>
       <c r="N13" s="1">
-        <v>105000</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -3577,16 +3579,16 @@
         <v>18</v>
       </c>
       <c r="K14" s="2">
-        <v>0.5384615384615384</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L14" s="1">
-        <v>0.1925925925925926</v>
+        <v>0.2923433874709977</v>
       </c>
       <c r="M14" s="1">
-        <v>130000</v>
+        <v>630000</v>
       </c>
       <c r="N14" s="1">
-        <v>70000</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -3597,16 +3599,16 @@
         <v>19</v>
       </c>
       <c r="K15" s="2">
-        <v>0.5526315789473685</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="L15" s="1">
-        <v>0.2567567567567567</v>
+        <v>0.2954048140043763</v>
       </c>
       <c r="M15" s="1">
-        <v>190000</v>
+        <v>675000</v>
       </c>
       <c r="N15" s="1">
-        <v>105000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3617,16 +3619,16 @@
         <v>20</v>
       </c>
       <c r="K16" s="2">
-        <v>0.6216216216216216</v>
+        <v>0.8706896551724138</v>
       </c>
       <c r="L16" s="1">
-        <v>0.2387096774193548</v>
+        <v>0.2516268980477224</v>
       </c>
       <c r="M16" s="1">
-        <v>185000</v>
+        <v>580000</v>
       </c>
       <c r="N16" s="1">
-        <v>115000</v>
+        <v>505000</v>
       </c>
     </row>
     <row r="17" spans="9:14">
@@ -3637,16 +3639,16 @@
         <v>8</v>
       </c>
       <c r="K17" s="2">
-        <v>0.1891891891891892</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="L17" s="1">
-        <v>0.3057851239669421</v>
+        <v>0.3959390862944163</v>
       </c>
       <c r="M17" s="1">
-        <v>185000</v>
+        <v>780000</v>
       </c>
       <c r="N17" s="1">
-        <v>35000</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="18" spans="9:14">
@@ -3657,16 +3659,16 @@
         <v>9</v>
       </c>
       <c r="K18" s="2">
-        <v>0.25</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="L18" s="1">
-        <v>0.3053435114503817</v>
+        <v>0.4195011337868481</v>
       </c>
       <c r="M18" s="1">
-        <v>200000</v>
+        <v>925000</v>
       </c>
       <c r="N18" s="1">
-        <v>50000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="19" spans="9:14">
@@ -3677,16 +3679,16 @@
         <v>10</v>
       </c>
       <c r="K19" s="2">
-        <v>0.2166666666666667</v>
+        <v>0.4943181818181818</v>
       </c>
       <c r="L19" s="1">
-        <v>0.3726708074534161</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="M19" s="1">
-        <v>300000</v>
+        <v>880000</v>
       </c>
       <c r="N19" s="1">
-        <v>65000</v>
+        <v>435000</v>
       </c>
     </row>
     <row r="20" spans="9:14">
@@ -3697,16 +3699,16 @@
         <v>11</v>
       </c>
       <c r="K20" s="2">
-        <v>0.2857142857142857</v>
+        <v>0.4539473684210527</v>
       </c>
       <c r="L20" s="1">
-        <v>0.4294478527607362</v>
+        <v>0.3326039387308534</v>
       </c>
       <c r="M20" s="1">
-        <v>350000</v>
+        <v>760000</v>
       </c>
       <c r="N20" s="1">
-        <v>100000</v>
+        <v>345000</v>
       </c>
     </row>
     <row r="21" spans="9:14">
@@ -3717,16 +3719,16 @@
         <v>12</v>
       </c>
       <c r="K21" s="2">
-        <v>0.2352941176470588</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="L21" s="1">
-        <v>0.3422818791946309</v>
+        <v>0.3363636363636364</v>
       </c>
       <c r="M21" s="1">
-        <v>255000</v>
+        <v>740000</v>
       </c>
       <c r="N21" s="1">
-        <v>60000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="22" spans="9:14">
@@ -3737,16 +3739,16 @@
         <v>13</v>
       </c>
       <c r="K22" s="2">
-        <v>0.1551724137931035</v>
+        <v>0.4802631578947368</v>
       </c>
       <c r="L22" s="1">
-        <v>0.3892617449664429</v>
+        <v>0.3734643734643734</v>
       </c>
       <c r="M22" s="1">
-        <v>290000</v>
+        <v>760000</v>
       </c>
       <c r="N22" s="1">
-        <v>45000</v>
+        <v>365000</v>
       </c>
     </row>
     <row r="23" spans="9:14">
@@ -3757,16 +3759,16 @@
         <v>14</v>
       </c>
       <c r="K23" s="2">
-        <v>0.1964285714285714</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="L23" s="1">
-        <v>0.3809523809523809</v>
+        <v>0.3485193621867881</v>
       </c>
       <c r="M23" s="1">
-        <v>280000</v>
+        <v>765000</v>
       </c>
       <c r="N23" s="1">
-        <v>55000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="24" spans="9:14">
@@ -3777,16 +3779,16 @@
         <v>15</v>
       </c>
       <c r="K24" s="2">
-        <v>0.2765957446808511</v>
+        <v>0.4796747967479675</v>
       </c>
       <c r="L24" s="1">
-        <v>0.3286713286713286</v>
+        <v>0.2992700729927008</v>
       </c>
       <c r="M24" s="1">
-        <v>235000</v>
+        <v>615000</v>
       </c>
       <c r="N24" s="1">
-        <v>65000</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="25" spans="9:14">
@@ -3797,16 +3799,16 @@
         <v>16</v>
       </c>
       <c r="K25" s="2">
-        <v>0.2549019607843137</v>
+        <v>0.456</v>
       </c>
       <c r="L25" s="1">
-        <v>0.3422818791946309</v>
+        <v>0.2955082742316785</v>
       </c>
       <c r="M25" s="1">
-        <v>255000</v>
+        <v>625000</v>
       </c>
       <c r="N25" s="1">
-        <v>65000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="26" spans="9:14">
@@ -3817,16 +3819,16 @@
         <v>17</v>
       </c>
       <c r="K26" s="2">
-        <v>0.2916666666666667</v>
+        <v>0.5528455284552846</v>
       </c>
       <c r="L26" s="1">
-        <v>0.3380281690140845</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="M26" s="1">
-        <v>240000</v>
+        <v>615000</v>
       </c>
       <c r="N26" s="1">
-        <v>70000</v>
+        <v>340000</v>
       </c>
     </row>
     <row r="27" spans="9:14">
@@ -3837,16 +3839,16 @@
         <v>18</v>
       </c>
       <c r="K27" s="2">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="1">
-        <v>0.237037037037037</v>
+        <v>0.2645011600928074</v>
       </c>
       <c r="M27" s="1">
-        <v>160000</v>
+        <v>570000</v>
       </c>
       <c r="N27" s="1">
-        <v>60000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="28" spans="9:14">
@@ -3857,16 +3859,16 @@
         <v>19</v>
       </c>
       <c r="K28" s="2">
-        <v>0.3333333333333333</v>
+        <v>0.5597014925373134</v>
       </c>
       <c r="L28" s="1">
-        <v>0.2635135135135135</v>
+        <v>0.2932166301969366</v>
       </c>
       <c r="M28" s="1">
-        <v>195000</v>
+        <v>670000</v>
       </c>
       <c r="N28" s="1">
-        <v>65000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="29" spans="9:14">
@@ -3877,16 +3879,16 @@
         <v>20</v>
       </c>
       <c r="K29" s="2">
-        <v>0.2380952380952381</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="L29" s="1">
-        <v>0.2709677419354839</v>
+        <v>0.3036876355748373</v>
       </c>
       <c r="M29" s="1">
-        <v>210000</v>
+        <v>700000</v>
       </c>
       <c r="N29" s="1">
-        <v>50000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="30" spans="9:14">
@@ -3897,16 +3899,16 @@
         <v>8</v>
       </c>
       <c r="K30" s="2">
-        <v>0.07692307692307693</v>
+        <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>0.1074380165289256</v>
+        <v>0.1421319796954315</v>
       </c>
       <c r="M30" s="1">
-        <v>65000</v>
+        <v>280000</v>
       </c>
       <c r="N30" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="9:14">
@@ -3917,16 +3919,16 @@
         <v>9</v>
       </c>
       <c r="K31" s="2">
-        <v>0.08333333333333333</v>
+        <v>0.07954545454545454</v>
       </c>
       <c r="L31" s="1">
-        <v>0.0916030534351145</v>
+        <v>0.199546485260771</v>
       </c>
       <c r="M31" s="1">
-        <v>60000</v>
+        <v>440000</v>
       </c>
       <c r="N31" s="1">
-        <v>5000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="32" spans="9:14">
@@ -3937,16 +3939,16 @@
         <v>10</v>
       </c>
       <c r="K32" s="2">
-        <v>0.1739130434782609</v>
+        <v>0.09174311926605505</v>
       </c>
       <c r="L32" s="1">
-        <v>0.1428571428571428</v>
+        <v>0.2523148148148148</v>
       </c>
       <c r="M32" s="1">
-        <v>115000</v>
+        <v>545000</v>
       </c>
       <c r="N32" s="1">
-        <v>20000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="33" spans="9:14">
@@ -3957,16 +3959,16 @@
         <v>11</v>
       </c>
       <c r="K33" s="2">
-        <v>0.2</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="L33" s="1">
-        <v>0.2147239263803681</v>
+        <v>0.3150984682713348</v>
       </c>
       <c r="M33" s="1">
-        <v>175000</v>
+        <v>720000</v>
       </c>
       <c r="N33" s="1">
-        <v>35000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="34" spans="9:14">
@@ -3977,16 +3979,16 @@
         <v>12</v>
       </c>
       <c r="K34" s="2">
-        <v>0.1282051282051282</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="L34" s="1">
-        <v>0.261744966442953</v>
+        <v>0.3022727272727272</v>
       </c>
       <c r="M34" s="1">
-        <v>195000</v>
+        <v>665000</v>
       </c>
       <c r="N34" s="1">
-        <v>25000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="35" spans="9:14">
@@ -3997,16 +3999,16 @@
         <v>13</v>
       </c>
       <c r="K35" s="2">
-        <v>0.1627906976744186</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="L35" s="1">
-        <v>0.2885906040268457</v>
+        <v>0.316953316953317</v>
       </c>
       <c r="M35" s="1">
-        <v>215000</v>
+        <v>645000</v>
       </c>
       <c r="N35" s="1">
-        <v>35000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="36" spans="9:14">
@@ -4017,16 +4019,16 @@
         <v>14</v>
       </c>
       <c r="K36" s="2">
-        <v>0.16</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="L36" s="1">
-        <v>0.3401360544217687</v>
+        <v>0.3280182232346242</v>
       </c>
       <c r="M36" s="1">
-        <v>250000</v>
+        <v>720000</v>
       </c>
       <c r="N36" s="1">
-        <v>40000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="37" spans="9:14">
@@ -4037,16 +4039,16 @@
         <v>15</v>
       </c>
       <c r="K37" s="2">
-        <v>0.09836065573770492</v>
+        <v>0.1059602649006623</v>
       </c>
       <c r="L37" s="1">
-        <v>0.4265734265734266</v>
+        <v>0.3673965936739659</v>
       </c>
       <c r="M37" s="1">
-        <v>305000</v>
+        <v>755000</v>
       </c>
       <c r="N37" s="1">
-        <v>30000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="38" spans="9:14">
@@ -4057,16 +4059,16 @@
         <v>16</v>
       </c>
       <c r="K38" s="2">
-        <v>0.1857142857142857</v>
+        <v>0.09580838323353294</v>
       </c>
       <c r="L38" s="1">
-        <v>0.4697986577181208</v>
+        <v>0.3947990543735225</v>
       </c>
       <c r="M38" s="1">
-        <v>350000</v>
+        <v>835000</v>
       </c>
       <c r="N38" s="1">
-        <v>65000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="39" spans="9:14">
@@ -4077,16 +4079,16 @@
         <v>17</v>
       </c>
       <c r="K39" s="2">
-        <v>0.180327868852459</v>
+        <v>0.09659090909090909</v>
       </c>
       <c r="L39" s="1">
-        <v>0.4295774647887324</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="M39" s="1">
-        <v>305000</v>
+        <v>880000</v>
       </c>
       <c r="N39" s="1">
-        <v>55000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="40" spans="9:14">
@@ -4097,16 +4099,16 @@
         <v>18</v>
       </c>
       <c r="K40" s="2">
-        <v>0.07792207792207792</v>
+        <v>0.1047120418848168</v>
       </c>
       <c r="L40" s="1">
-        <v>0.5703703703703704</v>
+        <v>0.4431554524361949</v>
       </c>
       <c r="M40" s="1">
-        <v>385000</v>
+        <v>955000</v>
       </c>
       <c r="N40" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="41" spans="9:14">
@@ -4117,16 +4119,16 @@
         <v>19</v>
       </c>
       <c r="K41" s="2">
-        <v>0.1267605633802817</v>
+        <v>0.1170212765957447</v>
       </c>
       <c r="L41" s="1">
-        <v>0.4797297297297297</v>
+        <v>0.4113785557986871</v>
       </c>
       <c r="M41" s="1">
-        <v>355000</v>
+        <v>940000</v>
       </c>
       <c r="N41" s="1">
-        <v>45000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="42" spans="9:14">
@@ -4137,16 +4139,16 @@
         <v>20</v>
       </c>
       <c r="K42" s="2">
-        <v>0.07894736842105263</v>
+        <v>0.07804878048780488</v>
       </c>
       <c r="L42" s="1">
-        <v>0.4903225806451613</v>
+        <v>0.4446854663774403</v>
       </c>
       <c r="M42" s="1">
-        <v>380000</v>
+        <v>1025000</v>
       </c>
       <c r="N42" s="1">
-        <v>30000</v>
+        <v>80000</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/pd_css_cross/Segments3_report.xlsx
+++ b/outputs/pd_css_cross/Segments3_report.xlsx
@@ -96,11 +96,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -144,11 +139,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -257,43 +249,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.8131868131868132</c:v>
+                  <c:v>0.8248587570621468</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9047619047619048</c:v>
+                  <c:v>0.9101796407185628</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9047619047619048</c:v>
+                  <c:v>0.9060402684563759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.937888198757764</c:v>
+                  <c:v>0.9358974358974359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9182389937106918</c:v>
+                  <c:v>0.9192546583850931</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9047619047619048</c:v>
+                  <c:v>0.8931297709923665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8873239436619719</c:v>
+                  <c:v>0.8802816901408451</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8686131386861314</c:v>
+                  <c:v>0.8666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.8625954198473282</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.881578947368421</c:v>
+                  <c:v>0.8782051282051282</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8095238095238095</c:v>
+                  <c:v>0.7906976744186046</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8222222222222222</c:v>
+                  <c:v>0.8270676691729323</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8706896551724138</c:v>
+                  <c:v>0.8869565217391304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -371,43 +363,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3269230769230769</c:v>
+                  <c:v>0.3333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4864864864864865</c:v>
+                  <c:v>0.4787234042553192</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4943181818181818</c:v>
+                  <c:v>0.4855491329479769</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4539473684210527</c:v>
+                  <c:v>0.4840764331210191</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5135135135135135</c:v>
+                  <c:v>0.5034013605442177</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4802631578947368</c:v>
+                  <c:v>0.4794520547945205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4901960784313725</c:v>
+                  <c:v>0.5033112582781457</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4796747967479675</c:v>
+                  <c:v>0.4803149606299212</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.456</c:v>
+                  <c:v>0.4634146341463415</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5528455284552846</c:v>
+                  <c:v>0.5508474576271186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5</c:v>
+                  <c:v>0.504424778761062</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5597014925373134</c:v>
+                  <c:v>0.5507246376811594</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5357142857142857</c:v>
+                  <c:v>0.524822695035461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -488,37 +480,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.07954545454545454</c:v>
+                  <c:v>0.08139534883720931</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.09174311926605505</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1458333333333333</c:v>
+                  <c:v>0.1319444444444444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1052631578947368</c:v>
+                  <c:v>0.1060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1395348837209302</c:v>
+                  <c:v>0.1384615384615385</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1458333333333333</c:v>
+                  <c:v>0.1438356164383562</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1059602649006623</c:v>
+                  <c:v>0.1073825503355705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.09580838323353294</c:v>
+                  <c:v>0.09467455621301775</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.09659090909090909</c:v>
+                  <c:v>0.096045197740113</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1047120418848168</c:v>
+                  <c:v>0.1058201058201058</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1170212765957447</c:v>
+                  <c:v>0.1182795698924731</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.07804878048780488</c:v>
@@ -699,43 +691,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.4619289340101523</c:v>
+                  <c:v>0.4492385786802031</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3809523809523809</c:v>
+                  <c:v>0.3786848072562358</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3402777777777778</c:v>
+                  <c:v>0.3449074074074074</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3522975929978118</c:v>
+                  <c:v>0.3413566739606127</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3613636363636364</c:v>
+                  <c:v>0.3659090909090909</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3095823095823096</c:v>
+                  <c:v>0.3218673218673219</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.3234624145785877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3333333333333333</c:v>
+                  <c:v>0.3284671532846715</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.3096926713947991</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3370288248337029</c:v>
+                  <c:v>0.3458980044345898</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2923433874709977</c:v>
+                  <c:v>0.2993039443155452</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2954048140043763</c:v>
+                  <c:v>0.2910284463894967</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2516268980477224</c:v>
+                  <c:v>0.2494577006507592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -813,43 +805,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3959390862944163</c:v>
+                  <c:v>0.4035532994923858</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4195011337868481</c:v>
+                  <c:v>0.4263038548752834</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4074074074074074</c:v>
+                  <c:v>0.400462962962963</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3326039387308534</c:v>
+                  <c:v>0.3435448577680525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3363636363636364</c:v>
+                  <c:v>0.3340909090909091</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3734643734643734</c:v>
+                  <c:v>0.3587223587223587</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3485193621867881</c:v>
+                  <c:v>0.3439635535307517</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2992700729927008</c:v>
+                  <c:v>0.3090024330900243</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2955082742316785</c:v>
+                  <c:v>0.2907801418439716</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2727272727272727</c:v>
+                  <c:v>0.2616407982261641</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2645011600928074</c:v>
+                  <c:v>0.2621809744779582</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2932166301969366</c:v>
+                  <c:v>0.3019693654266958</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3036876355748373</c:v>
+                  <c:v>0.3058568329718004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -927,40 +919,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1421319796954315</c:v>
+                  <c:v>0.1472081218274112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.199546485260771</c:v>
+                  <c:v>0.1950113378684807</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2523148148148148</c:v>
+                  <c:v>0.2546296296296297</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.3150984682713348</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3022727272727272</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.316953316953317</c:v>
+                  <c:v>0.3194103194103194</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3280182232346242</c:v>
+                  <c:v>0.3325740318906606</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3673965936739659</c:v>
+                  <c:v>0.3625304136253041</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3947990543735225</c:v>
+                  <c:v>0.3995271867612293</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3902439024390244</c:v>
+                  <c:v>0.3924611973392461</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4431554524361949</c:v>
+                  <c:v>0.4385150812064965</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4113785557986871</c:v>
+                  <c:v>0.4070021881838075</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.4446854663774403</c:v>
@@ -1141,43 +1133,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.8131868131868132</c:v>
+                  <c:v>0.8248587570621468</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9047619047619048</c:v>
+                  <c:v>0.9101796407185628</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9047619047619048</c:v>
+                  <c:v>0.9060402684563759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.937888198757764</c:v>
+                  <c:v>0.9358974358974359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9182389937106918</c:v>
+                  <c:v>0.9192546583850931</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9047619047619048</c:v>
+                  <c:v>0.8931297709923665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8873239436619719</c:v>
+                  <c:v>0.8802816901408451</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8686131386861314</c:v>
+                  <c:v>0.8666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.8625954198473282</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.881578947368421</c:v>
+                  <c:v>0.8782051282051282</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8095238095238095</c:v>
+                  <c:v>0.7906976744186046</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8222222222222222</c:v>
+                  <c:v>0.8270676691729323</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8706896551724138</c:v>
+                  <c:v>0.8869565217391304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1255,43 +1247,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3269230769230769</c:v>
+                  <c:v>0.3333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4864864864864865</c:v>
+                  <c:v>0.4787234042553192</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4943181818181818</c:v>
+                  <c:v>0.4855491329479769</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4539473684210527</c:v>
+                  <c:v>0.4840764331210191</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5135135135135135</c:v>
+                  <c:v>0.5034013605442177</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4802631578947368</c:v>
+                  <c:v>0.4794520547945205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4901960784313725</c:v>
+                  <c:v>0.5033112582781457</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4796747967479675</c:v>
+                  <c:v>0.4803149606299212</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.456</c:v>
+                  <c:v>0.4634146341463415</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5528455284552846</c:v>
+                  <c:v>0.5508474576271186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5</c:v>
+                  <c:v>0.504424778761062</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5597014925373134</c:v>
+                  <c:v>0.5507246376811594</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5357142857142857</c:v>
+                  <c:v>0.524822695035461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1372,37 +1364,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.07954545454545454</c:v>
+                  <c:v>0.08139534883720931</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.09174311926605505</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1458333333333333</c:v>
+                  <c:v>0.1319444444444444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1052631578947368</c:v>
+                  <c:v>0.1060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1395348837209302</c:v>
+                  <c:v>0.1384615384615385</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1458333333333333</c:v>
+                  <c:v>0.1438356164383562</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1059602649006623</c:v>
+                  <c:v>0.1073825503355705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.09580838323353294</c:v>
+                  <c:v>0.09467455621301775</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.09659090909090909</c:v>
+                  <c:v>0.096045197740113</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1047120418848168</c:v>
+                  <c:v>0.1058201058201058</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1170212765957447</c:v>
+                  <c:v>0.1182795698924731</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.07804878048780488</c:v>
@@ -1583,43 +1575,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.4619289340101523</c:v>
+                  <c:v>0.4492385786802031</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3809523809523809</c:v>
+                  <c:v>0.3786848072562358</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3402777777777778</c:v>
+                  <c:v>0.3449074074074074</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3522975929978118</c:v>
+                  <c:v>0.3413566739606127</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3613636363636364</c:v>
+                  <c:v>0.3659090909090909</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3095823095823096</c:v>
+                  <c:v>0.3218673218673219</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.3234624145785877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3333333333333333</c:v>
+                  <c:v>0.3284671532846715</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.3096926713947991</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3370288248337029</c:v>
+                  <c:v>0.3458980044345898</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2923433874709977</c:v>
+                  <c:v>0.2993039443155452</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2954048140043763</c:v>
+                  <c:v>0.2910284463894967</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2516268980477224</c:v>
+                  <c:v>0.2494577006507592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1697,43 +1689,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3959390862944163</c:v>
+                  <c:v>0.4035532994923858</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4195011337868481</c:v>
+                  <c:v>0.4263038548752834</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4074074074074074</c:v>
+                  <c:v>0.400462962962963</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3326039387308534</c:v>
+                  <c:v>0.3435448577680525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3363636363636364</c:v>
+                  <c:v>0.3340909090909091</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3734643734643734</c:v>
+                  <c:v>0.3587223587223587</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3485193621867881</c:v>
+                  <c:v>0.3439635535307517</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2992700729927008</c:v>
+                  <c:v>0.3090024330900243</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2955082742316785</c:v>
+                  <c:v>0.2907801418439716</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2727272727272727</c:v>
+                  <c:v>0.2616407982261641</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2645011600928074</c:v>
+                  <c:v>0.2621809744779582</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2932166301969366</c:v>
+                  <c:v>0.3019693654266958</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3036876355748373</c:v>
+                  <c:v>0.3058568329718004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,40 +1803,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1421319796954315</c:v>
+                  <c:v>0.1472081218274112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.199546485260771</c:v>
+                  <c:v>0.1950113378684807</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2523148148148148</c:v>
+                  <c:v>0.2546296296296297</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.3150984682713348</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3022727272727272</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.316953316953317</c:v>
+                  <c:v>0.3194103194103194</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3280182232346242</c:v>
+                  <c:v>0.3325740318906606</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3673965936739659</c:v>
+                  <c:v>0.3625304136253041</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3947990543735225</c:v>
+                  <c:v>0.3995271867612293</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3902439024390244</c:v>
+                  <c:v>0.3924611973392461</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4431554524361949</c:v>
+                  <c:v>0.4385150812064965</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4113785557986871</c:v>
+                  <c:v>0.4070021881838075</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.4446854663774403</c:v>
@@ -1937,8 +1929,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1967,8 +1959,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -2002,8 +1994,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -2032,8 +2024,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -2345,899 +2337,893 @@
   <dimension ref="A3:N42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="10.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="12" width="21.7109375" style="2" customWidth="1"/>
-    <col min="13" max="14" width="10.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="7" width="10.7109375" customWidth="1"/>
+    <col min="9" max="14" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:14">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>0</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.9502345014917034</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8.014037340297495</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="B4">
+        <v>0.9545565931879846</v>
+      </c>
+      <c r="C4">
+        <v>8.107875986233042</v>
+      </c>
+      <c r="D4">
         <v>0.8767268862911796</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>0.3334514528703048</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4">
         <v>1882</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4">
         <v>1650</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4">
         <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2">
-        <v>0.8131868131868132</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0.4619289340101523</v>
-      </c>
-      <c r="M4" s="3">
-        <v>182</v>
-      </c>
-      <c r="N4" s="3">
-        <v>148</v>
+      <c r="K4">
+        <v>0.8248587570621468</v>
+      </c>
+      <c r="L4">
+        <v>0.4492385786802031</v>
+      </c>
+      <c r="M4">
+        <v>177</v>
+      </c>
+      <c r="N4">
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
-        <v>-1.043918035281563</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.9500194933372372</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.4848484848484849</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="B5">
+        <v>-1.0100583376388</v>
+      </c>
+      <c r="C5">
+        <v>0.9491980724600928</v>
+      </c>
+      <c r="D5">
+        <v>0.4853801169590643</v>
+      </c>
+      <c r="E5">
         <v>0.3332742735648476</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>1881</v>
       </c>
-      <c r="G5" s="3">
-        <v>912</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="G5">
+        <v>913</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
       <c r="J5" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="2">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="M5" s="3">
-        <v>168</v>
-      </c>
-      <c r="N5" s="3">
+      <c r="K5">
+        <v>0.9101796407185628</v>
+      </c>
+      <c r="L5">
+        <v>0.3786848072562358</v>
+      </c>
+      <c r="M5">
+        <v>167</v>
+      </c>
+      <c r="N5">
         <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
-        <v>-10.8317280747611</v>
-      </c>
-      <c r="C6" s="1">
-        <v>-1.045108577584102</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="B6">
+        <v>-10.75813788412185</v>
+      </c>
+      <c r="C6">
+        <v>-1.010537872244683</v>
+      </c>
+      <c r="D6">
+        <v>0.1047315257841574</v>
+      </c>
+      <c r="E6">
         <v>0.3332742735648476</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>1881</v>
       </c>
-      <c r="G6" s="3">
-        <v>198</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="G6">
+        <v>197</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="2">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0.3402777777777778</v>
-      </c>
-      <c r="M6" s="3">
-        <v>147</v>
-      </c>
-      <c r="N6" s="3">
-        <v>133</v>
+      <c r="K6">
+        <v>0.9060402684563759</v>
+      </c>
+      <c r="L6">
+        <v>0.3449074074074074</v>
+      </c>
+      <c r="M6">
+        <v>149</v>
+      </c>
+      <c r="N6">
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="I7" s="1">
+      <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="2">
-        <v>0.937888198757764</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0.3522975929978118</v>
-      </c>
-      <c r="M7" s="3">
-        <v>161</v>
-      </c>
-      <c r="N7" s="3">
-        <v>151</v>
+      <c r="K7">
+        <v>0.9358974358974359</v>
+      </c>
+      <c r="L7">
+        <v>0.3413566739606127</v>
+      </c>
+      <c r="M7">
+        <v>156</v>
+      </c>
+      <c r="N7">
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="I8" s="1">
+      <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="2">
-        <v>0.9182389937106918</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0.3613636363636364</v>
-      </c>
-      <c r="M8" s="3">
-        <v>159</v>
-      </c>
-      <c r="N8" s="3">
-        <v>146</v>
+      <c r="K8">
+        <v>0.9192546583850931</v>
+      </c>
+      <c r="L8">
+        <v>0.3659090909090909</v>
+      </c>
+      <c r="M8">
+        <v>161</v>
+      </c>
+      <c r="N8">
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="I9" s="1">
+      <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="2">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0.3095823095823096</v>
-      </c>
-      <c r="M9" s="3">
-        <v>126</v>
-      </c>
-      <c r="N9" s="3">
-        <v>114</v>
+      <c r="K9">
+        <v>0.8931297709923665</v>
+      </c>
+      <c r="L9">
+        <v>0.3218673218673219</v>
+      </c>
+      <c r="M9">
+        <v>131</v>
+      </c>
+      <c r="N9">
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="I10" s="1">
+      <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="2">
-        <v>0.8873239436619719</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="K10">
+        <v>0.8802816901408451</v>
+      </c>
+      <c r="L10">
         <v>0.3234624145785877</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10">
         <v>142</v>
       </c>
-      <c r="N10" s="3">
-        <v>126</v>
+      <c r="N10">
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="I11" s="1">
+      <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="2">
-        <v>0.8686131386861314</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="M11" s="3">
-        <v>137</v>
-      </c>
-      <c r="N11" s="3">
-        <v>119</v>
+      <c r="K11">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L11">
+        <v>0.3284671532846715</v>
+      </c>
+      <c r="M11">
+        <v>135</v>
+      </c>
+      <c r="N11">
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="I12" s="1">
+      <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12">
         <v>0.8625954198473282</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12">
         <v>0.3096926713947991</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12">
         <v>131</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12">
         <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="I13" s="1">
+      <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="2">
-        <v>0.881578947368421</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0.3370288248337029</v>
-      </c>
-      <c r="M13" s="3">
-        <v>152</v>
-      </c>
-      <c r="N13" s="3">
-        <v>134</v>
+      <c r="K13">
+        <v>0.8782051282051282</v>
+      </c>
+      <c r="L13">
+        <v>0.3458980044345898</v>
+      </c>
+      <c r="M13">
+        <v>156</v>
+      </c>
+      <c r="N13">
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="I14" s="1">
+      <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="2">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="L14" s="2">
-        <v>0.2923433874709977</v>
-      </c>
-      <c r="M14" s="3">
-        <v>126</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="K14">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="L14">
+        <v>0.2993039443155452</v>
+      </c>
+      <c r="M14">
+        <v>129</v>
+      </c>
+      <c r="N14">
         <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="I15" s="1">
+      <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="2">
-        <v>0.8222222222222222</v>
-      </c>
-      <c r="L15" s="2">
-        <v>0.2954048140043763</v>
-      </c>
-      <c r="M15" s="3">
-        <v>135</v>
-      </c>
-      <c r="N15" s="3">
-        <v>111</v>
+      <c r="K15">
+        <v>0.8270676691729323</v>
+      </c>
+      <c r="L15">
+        <v>0.2910284463894967</v>
+      </c>
+      <c r="M15">
+        <v>133</v>
+      </c>
+      <c r="N15">
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="I16" s="1">
+      <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="2">
-        <v>0.8706896551724138</v>
-      </c>
-      <c r="L16" s="2">
-        <v>0.2516268980477224</v>
-      </c>
-      <c r="M16" s="3">
-        <v>116</v>
-      </c>
-      <c r="N16" s="3">
-        <v>101</v>
+      <c r="K16">
+        <v>0.8869565217391304</v>
+      </c>
+      <c r="L16">
+        <v>0.2494577006507592</v>
+      </c>
+      <c r="M16">
+        <v>115</v>
+      </c>
+      <c r="N16">
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="9:14">
-      <c r="I17" s="1">
+      <c r="I17">
         <v>1</v>
       </c>
       <c r="J17" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="2">
-        <v>0.3269230769230769</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0.3959390862944163</v>
-      </c>
-      <c r="M17" s="3">
-        <v>156</v>
-      </c>
-      <c r="N17" s="3">
-        <v>51</v>
+      <c r="K17">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L17">
+        <v>0.4035532994923858</v>
+      </c>
+      <c r="M17">
+        <v>159</v>
+      </c>
+      <c r="N17">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="9:14">
-      <c r="I18" s="1">
+      <c r="I18">
         <v>1</v>
       </c>
       <c r="J18" t="s">
         <v>9</v>
       </c>
-      <c r="K18" s="2">
-        <v>0.4864864864864865</v>
-      </c>
-      <c r="L18" s="2">
-        <v>0.4195011337868481</v>
-      </c>
-      <c r="M18" s="3">
-        <v>185</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="K18">
+        <v>0.4787234042553192</v>
+      </c>
+      <c r="L18">
+        <v>0.4263038548752834</v>
+      </c>
+      <c r="M18">
+        <v>188</v>
+      </c>
+      <c r="N18">
         <v>90</v>
       </c>
     </row>
     <row r="19" spans="9:14">
-      <c r="I19" s="1">
+      <c r="I19">
         <v>1</v>
       </c>
       <c r="J19" t="s">
         <v>10</v>
       </c>
-      <c r="K19" s="2">
-        <v>0.4943181818181818</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="M19" s="3">
-        <v>176</v>
-      </c>
-      <c r="N19" s="3">
-        <v>87</v>
+      <c r="K19">
+        <v>0.4855491329479769</v>
+      </c>
+      <c r="L19">
+        <v>0.400462962962963</v>
+      </c>
+      <c r="M19">
+        <v>173</v>
+      </c>
+      <c r="N19">
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="9:14">
-      <c r="I20" s="1">
+      <c r="I20">
         <v>1</v>
       </c>
       <c r="J20" t="s">
         <v>11</v>
       </c>
-      <c r="K20" s="2">
-        <v>0.4539473684210527</v>
-      </c>
-      <c r="L20" s="2">
-        <v>0.3326039387308534</v>
-      </c>
-      <c r="M20" s="3">
-        <v>152</v>
-      </c>
-      <c r="N20" s="3">
-        <v>69</v>
+      <c r="K20">
+        <v>0.4840764331210191</v>
+      </c>
+      <c r="L20">
+        <v>0.3435448577680525</v>
+      </c>
+      <c r="M20">
+        <v>157</v>
+      </c>
+      <c r="N20">
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="9:14">
-      <c r="I21" s="1">
+      <c r="I21">
         <v>1</v>
       </c>
       <c r="J21" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="2">
-        <v>0.5135135135135135</v>
-      </c>
-      <c r="L21" s="2">
-        <v>0.3363636363636364</v>
-      </c>
-      <c r="M21" s="3">
-        <v>148</v>
-      </c>
-      <c r="N21" s="3">
-        <v>76</v>
+      <c r="K21">
+        <v>0.5034013605442177</v>
+      </c>
+      <c r="L21">
+        <v>0.3340909090909091</v>
+      </c>
+      <c r="M21">
+        <v>147</v>
+      </c>
+      <c r="N21">
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="9:14">
-      <c r="I22" s="1">
+      <c r="I22">
         <v>1</v>
       </c>
       <c r="J22" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="2">
-        <v>0.4802631578947368</v>
-      </c>
-      <c r="L22" s="2">
-        <v>0.3734643734643734</v>
-      </c>
-      <c r="M22" s="3">
-        <v>152</v>
-      </c>
-      <c r="N22" s="3">
-        <v>73</v>
+      <c r="K22">
+        <v>0.4794520547945205</v>
+      </c>
+      <c r="L22">
+        <v>0.3587223587223587</v>
+      </c>
+      <c r="M22">
+        <v>146</v>
+      </c>
+      <c r="N22">
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="9:14">
-      <c r="I23" s="1">
+      <c r="I23">
         <v>1</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="2">
-        <v>0.4901960784313725</v>
-      </c>
-      <c r="L23" s="2">
-        <v>0.3485193621867881</v>
-      </c>
-      <c r="M23" s="3">
-        <v>153</v>
-      </c>
-      <c r="N23" s="3">
-        <v>75</v>
+      <c r="K23">
+        <v>0.5033112582781457</v>
+      </c>
+      <c r="L23">
+        <v>0.3439635535307517</v>
+      </c>
+      <c r="M23">
+        <v>151</v>
+      </c>
+      <c r="N23">
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="9:14">
-      <c r="I24" s="1">
+      <c r="I24">
         <v>1</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
-      <c r="K24" s="2">
-        <v>0.4796747967479675</v>
-      </c>
-      <c r="L24" s="2">
-        <v>0.2992700729927008</v>
-      </c>
-      <c r="M24" s="3">
-        <v>123</v>
-      </c>
-      <c r="N24" s="3">
-        <v>59</v>
+      <c r="K24">
+        <v>0.4803149606299212</v>
+      </c>
+      <c r="L24">
+        <v>0.3090024330900243</v>
+      </c>
+      <c r="M24">
+        <v>127</v>
+      </c>
+      <c r="N24">
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="9:14">
-      <c r="I25" s="1">
+      <c r="I25">
         <v>1</v>
       </c>
       <c r="J25" t="s">
         <v>16</v>
       </c>
-      <c r="K25" s="2">
-        <v>0.456</v>
-      </c>
-      <c r="L25" s="2">
-        <v>0.2955082742316785</v>
-      </c>
-      <c r="M25" s="3">
-        <v>125</v>
-      </c>
-      <c r="N25" s="3">
+      <c r="K25">
+        <v>0.4634146341463415</v>
+      </c>
+      <c r="L25">
+        <v>0.2907801418439716</v>
+      </c>
+      <c r="M25">
+        <v>123</v>
+      </c>
+      <c r="N25">
         <v>57</v>
       </c>
     </row>
     <row r="26" spans="9:14">
-      <c r="I26" s="1">
+      <c r="I26">
         <v>1</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
       </c>
-      <c r="K26" s="2">
-        <v>0.5528455284552846</v>
-      </c>
-      <c r="L26" s="2">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="M26" s="3">
-        <v>123</v>
-      </c>
-      <c r="N26" s="3">
-        <v>68</v>
+      <c r="K26">
+        <v>0.5508474576271186</v>
+      </c>
+      <c r="L26">
+        <v>0.2616407982261641</v>
+      </c>
+      <c r="M26">
+        <v>118</v>
+      </c>
+      <c r="N26">
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="9:14">
-      <c r="I27" s="1">
+      <c r="I27">
         <v>1</v>
       </c>
       <c r="J27" t="s">
         <v>18</v>
       </c>
-      <c r="K27" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0.2645011600928074</v>
-      </c>
-      <c r="M27" s="3">
-        <v>114</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="K27">
+        <v>0.504424778761062</v>
+      </c>
+      <c r="L27">
+        <v>0.2621809744779582</v>
+      </c>
+      <c r="M27">
+        <v>113</v>
+      </c>
+      <c r="N27">
         <v>57</v>
       </c>
     </row>
     <row r="28" spans="9:14">
-      <c r="I28" s="1">
+      <c r="I28">
         <v>1</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
       </c>
-      <c r="K28" s="2">
-        <v>0.5597014925373134</v>
-      </c>
-      <c r="L28" s="2">
-        <v>0.2932166301969366</v>
-      </c>
-      <c r="M28" s="3">
-        <v>134</v>
-      </c>
-      <c r="N28" s="3">
-        <v>75</v>
+      <c r="K28">
+        <v>0.5507246376811594</v>
+      </c>
+      <c r="L28">
+        <v>0.3019693654266958</v>
+      </c>
+      <c r="M28">
+        <v>138</v>
+      </c>
+      <c r="N28">
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="9:14">
-      <c r="I29" s="1">
+      <c r="I29">
         <v>1</v>
       </c>
       <c r="J29" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="2">
-        <v>0.5357142857142857</v>
-      </c>
-      <c r="L29" s="2">
-        <v>0.3036876355748373</v>
-      </c>
-      <c r="M29" s="3">
-        <v>140</v>
-      </c>
-      <c r="N29" s="3">
-        <v>75</v>
+      <c r="K29">
+        <v>0.524822695035461</v>
+      </c>
+      <c r="L29">
+        <v>0.3058568329718004</v>
+      </c>
+      <c r="M29">
+        <v>141</v>
+      </c>
+      <c r="N29">
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="9:14">
-      <c r="I30" s="1">
+      <c r="I30">
         <v>2</v>
       </c>
       <c r="J30" t="s">
         <v>8</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="2">
-        <v>0.1421319796954315</v>
-      </c>
-      <c r="M30" s="3">
-        <v>56</v>
-      </c>
-      <c r="N30" s="3">
+      <c r="L30">
+        <v>0.1472081218274112</v>
+      </c>
+      <c r="M30">
+        <v>58</v>
+      </c>
+      <c r="N30">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="9:14">
-      <c r="I31" s="1">
+      <c r="I31">
         <v>2</v>
       </c>
       <c r="J31" t="s">
         <v>9</v>
       </c>
-      <c r="K31" s="2">
-        <v>0.07954545454545454</v>
-      </c>
-      <c r="L31" s="2">
-        <v>0.199546485260771</v>
-      </c>
-      <c r="M31" s="3">
-        <v>88</v>
-      </c>
-      <c r="N31" s="3">
+      <c r="K31">
+        <v>0.08139534883720931</v>
+      </c>
+      <c r="L31">
+        <v>0.1950113378684807</v>
+      </c>
+      <c r="M31">
+        <v>86</v>
+      </c>
+      <c r="N31">
         <v>7</v>
       </c>
     </row>
     <row r="32" spans="9:14">
-      <c r="I32" s="1">
+      <c r="I32">
         <v>2</v>
       </c>
       <c r="J32" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="2">
-        <v>0.09174311926605505</v>
-      </c>
-      <c r="L32" s="2">
-        <v>0.2523148148148148</v>
-      </c>
-      <c r="M32" s="3">
-        <v>109</v>
-      </c>
-      <c r="N32" s="3">
-        <v>10</v>
+      <c r="K32">
+        <v>0.1</v>
+      </c>
+      <c r="L32">
+        <v>0.2546296296296297</v>
+      </c>
+      <c r="M32">
+        <v>110</v>
+      </c>
+      <c r="N32">
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="9:14">
-      <c r="I33" s="1">
+      <c r="I33">
         <v>2</v>
       </c>
       <c r="J33" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="2">
-        <v>0.1458333333333333</v>
-      </c>
-      <c r="L33" s="2">
+      <c r="K33">
+        <v>0.1319444444444444</v>
+      </c>
+      <c r="L33">
         <v>0.3150984682713348</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33">
         <v>144</v>
       </c>
-      <c r="N33" s="3">
-        <v>21</v>
+      <c r="N33">
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="9:14">
-      <c r="I34" s="1">
+      <c r="I34">
         <v>2</v>
       </c>
       <c r="J34" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="2">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="L34" s="2">
-        <v>0.3022727272727272</v>
-      </c>
-      <c r="M34" s="3">
-        <v>133</v>
-      </c>
-      <c r="N34" s="3">
+      <c r="K34">
+        <v>0.1060606060606061</v>
+      </c>
+      <c r="L34">
+        <v>0.3</v>
+      </c>
+      <c r="M34">
+        <v>132</v>
+      </c>
+      <c r="N34">
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="9:14">
-      <c r="I35" s="1">
+      <c r="I35">
         <v>2</v>
       </c>
       <c r="J35" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="2">
-        <v>0.1395348837209302</v>
-      </c>
-      <c r="L35" s="2">
-        <v>0.316953316953317</v>
-      </c>
-      <c r="M35" s="3">
-        <v>129</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="K35">
+        <v>0.1384615384615385</v>
+      </c>
+      <c r="L35">
+        <v>0.3194103194103194</v>
+      </c>
+      <c r="M35">
+        <v>130</v>
+      </c>
+      <c r="N35">
         <v>18</v>
       </c>
     </row>
     <row r="36" spans="9:14">
-      <c r="I36" s="1">
+      <c r="I36">
         <v>2</v>
       </c>
       <c r="J36" t="s">
         <v>14</v>
       </c>
-      <c r="K36" s="2">
-        <v>0.1458333333333333</v>
-      </c>
-      <c r="L36" s="2">
-        <v>0.3280182232346242</v>
-      </c>
-      <c r="M36" s="3">
-        <v>144</v>
-      </c>
-      <c r="N36" s="3">
+      <c r="K36">
+        <v>0.1438356164383562</v>
+      </c>
+      <c r="L36">
+        <v>0.3325740318906606</v>
+      </c>
+      <c r="M36">
+        <v>146</v>
+      </c>
+      <c r="N36">
         <v>21</v>
       </c>
     </row>
     <row r="37" spans="9:14">
-      <c r="I37" s="1">
+      <c r="I37">
         <v>2</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
-      <c r="K37" s="2">
-        <v>0.1059602649006623</v>
-      </c>
-      <c r="L37" s="2">
-        <v>0.3673965936739659</v>
-      </c>
-      <c r="M37" s="3">
-        <v>151</v>
-      </c>
-      <c r="N37" s="3">
+      <c r="K37">
+        <v>0.1073825503355705</v>
+      </c>
+      <c r="L37">
+        <v>0.3625304136253041</v>
+      </c>
+      <c r="M37">
+        <v>149</v>
+      </c>
+      <c r="N37">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="9:14">
-      <c r="I38" s="1">
+      <c r="I38">
         <v>2</v>
       </c>
       <c r="J38" t="s">
         <v>16</v>
       </c>
-      <c r="K38" s="2">
-        <v>0.09580838323353294</v>
-      </c>
-      <c r="L38" s="2">
-        <v>0.3947990543735225</v>
-      </c>
-      <c r="M38" s="3">
-        <v>167</v>
-      </c>
-      <c r="N38" s="3">
+      <c r="K38">
+        <v>0.09467455621301775</v>
+      </c>
+      <c r="L38">
+        <v>0.3995271867612293</v>
+      </c>
+      <c r="M38">
+        <v>169</v>
+      </c>
+      <c r="N38">
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="9:14">
-      <c r="I39" s="1">
+      <c r="I39">
         <v>2</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
       </c>
-      <c r="K39" s="2">
-        <v>0.09659090909090909</v>
-      </c>
-      <c r="L39" s="2">
-        <v>0.3902439024390244</v>
-      </c>
-      <c r="M39" s="3">
-        <v>176</v>
-      </c>
-      <c r="N39" s="3">
+      <c r="K39">
+        <v>0.096045197740113</v>
+      </c>
+      <c r="L39">
+        <v>0.3924611973392461</v>
+      </c>
+      <c r="M39">
+        <v>177</v>
+      </c>
+      <c r="N39">
         <v>17</v>
       </c>
     </row>
     <row r="40" spans="9:14">
-      <c r="I40" s="1">
+      <c r="I40">
         <v>2</v>
       </c>
       <c r="J40" t="s">
         <v>18</v>
       </c>
-      <c r="K40" s="2">
-        <v>0.1047120418848168</v>
-      </c>
-      <c r="L40" s="2">
-        <v>0.4431554524361949</v>
-      </c>
-      <c r="M40" s="3">
-        <v>191</v>
-      </c>
-      <c r="N40" s="3">
+      <c r="K40">
+        <v>0.1058201058201058</v>
+      </c>
+      <c r="L40">
+        <v>0.4385150812064965</v>
+      </c>
+      <c r="M40">
+        <v>189</v>
+      </c>
+      <c r="N40">
         <v>20</v>
       </c>
     </row>
     <row r="41" spans="9:14">
-      <c r="I41" s="1">
+      <c r="I41">
         <v>2</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
       </c>
-      <c r="K41" s="2">
-        <v>0.1170212765957447</v>
-      </c>
-      <c r="L41" s="2">
-        <v>0.4113785557986871</v>
-      </c>
-      <c r="M41" s="3">
-        <v>188</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="K41">
+        <v>0.1182795698924731</v>
+      </c>
+      <c r="L41">
+        <v>0.4070021881838075</v>
+      </c>
+      <c r="M41">
+        <v>186</v>
+      </c>
+      <c r="N41">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="9:14">
-      <c r="I42" s="1">
+      <c r="I42">
         <v>2</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="2">
+      <c r="K42">
         <v>0.07804878048780488</v>
       </c>
-      <c r="L42" s="2">
+      <c r="L42">
         <v>0.4446854663774403</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42">
         <v>205</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42">
         <v>16</v>
       </c>
     </row>
@@ -3252,902 +3238,899 @@
   <dimension ref="A3:N42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="9" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:14">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>0</v>
       </c>
-      <c r="B4" s="1">
-        <v>0.9502345014917034</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8.014037340297495</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="B4">
+        <v>0.9545565931879846</v>
+      </c>
+      <c r="C4">
+        <v>8.107875986233042</v>
+      </c>
+      <c r="D4">
         <v>0.8767268862911796</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>0.3334514528703048</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>9410000</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>8250000</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4">
         <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2">
-        <v>0.8131868131868132</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0.4619289340101523</v>
-      </c>
-      <c r="M4" s="1">
-        <v>910000</v>
-      </c>
-      <c r="N4" s="1">
-        <v>740000</v>
+      <c r="K4">
+        <v>0.8248587570621468</v>
+      </c>
+      <c r="L4">
+        <v>0.4492385786802031</v>
+      </c>
+      <c r="M4">
+        <v>885000</v>
+      </c>
+      <c r="N4">
+        <v>730000</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
-        <v>-1.043918035281563</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.9500194933372372</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.4848484848484849</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="B5">
+        <v>-1.0100583376388</v>
+      </c>
+      <c r="C5">
+        <v>0.9491980724600928</v>
+      </c>
+      <c r="D5">
+        <v>0.4853801169590643</v>
+      </c>
+      <c r="E5">
         <v>0.3332742735648476</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>9405000</v>
       </c>
-      <c r="G5" s="1">
-        <v>4560000</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="G5">
+        <v>4565000</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
       <c r="J5" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="2">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="M5" s="1">
-        <v>840000</v>
-      </c>
-      <c r="N5" s="1">
+      <c r="K5">
+        <v>0.9101796407185628</v>
+      </c>
+      <c r="L5">
+        <v>0.3786848072562358</v>
+      </c>
+      <c r="M5">
+        <v>835000</v>
+      </c>
+      <c r="N5">
         <v>760000</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
-        <v>-10.8317280747611</v>
-      </c>
-      <c r="C6" s="1">
-        <v>-1.045108577584102</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="B6">
+        <v>-10.75813788412185</v>
+      </c>
+      <c r="C6">
+        <v>-1.010537872244683</v>
+      </c>
+      <c r="D6">
+        <v>0.1047315257841574</v>
+      </c>
+      <c r="E6">
         <v>0.3332742735648476</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>9405000</v>
       </c>
-      <c r="G6" s="1">
-        <v>990000</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="G6">
+        <v>985000</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="2">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0.3402777777777778</v>
-      </c>
-      <c r="M6" s="1">
-        <v>735000</v>
-      </c>
-      <c r="N6" s="1">
-        <v>665000</v>
+      <c r="K6">
+        <v>0.9060402684563759</v>
+      </c>
+      <c r="L6">
+        <v>0.3449074074074074</v>
+      </c>
+      <c r="M6">
+        <v>745000</v>
+      </c>
+      <c r="N6">
+        <v>675000</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="I7" s="1">
+      <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="2">
-        <v>0.937888198757764</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0.3522975929978118</v>
-      </c>
-      <c r="M7" s="1">
-        <v>805000</v>
-      </c>
-      <c r="N7" s="1">
-        <v>755000</v>
+      <c r="K7">
+        <v>0.9358974358974359</v>
+      </c>
+      <c r="L7">
+        <v>0.3413566739606127</v>
+      </c>
+      <c r="M7">
+        <v>780000</v>
+      </c>
+      <c r="N7">
+        <v>730000</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="I8" s="1">
+      <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="2">
-        <v>0.9182389937106918</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0.3613636363636364</v>
-      </c>
-      <c r="M8" s="1">
-        <v>795000</v>
-      </c>
-      <c r="N8" s="1">
-        <v>730000</v>
+      <c r="K8">
+        <v>0.9192546583850931</v>
+      </c>
+      <c r="L8">
+        <v>0.3659090909090909</v>
+      </c>
+      <c r="M8">
+        <v>805000</v>
+      </c>
+      <c r="N8">
+        <v>740000</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="I9" s="1">
+      <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="2">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0.3095823095823096</v>
-      </c>
-      <c r="M9" s="1">
-        <v>630000</v>
-      </c>
-      <c r="N9" s="1">
-        <v>570000</v>
+      <c r="K9">
+        <v>0.8931297709923665</v>
+      </c>
+      <c r="L9">
+        <v>0.3218673218673219</v>
+      </c>
+      <c r="M9">
+        <v>655000</v>
+      </c>
+      <c r="N9">
+        <v>585000</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="I10" s="1">
+      <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="2">
-        <v>0.8873239436619719</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K10">
+        <v>0.8802816901408451</v>
+      </c>
+      <c r="L10">
         <v>0.3234624145785877</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10">
         <v>710000</v>
       </c>
-      <c r="N10" s="1">
-        <v>630000</v>
+      <c r="N10">
+        <v>625000</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="I11" s="1">
+      <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="2">
-        <v>0.8686131386861314</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="M11" s="1">
-        <v>685000</v>
-      </c>
-      <c r="N11" s="1">
-        <v>595000</v>
+      <c r="K11">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L11">
+        <v>0.3284671532846715</v>
+      </c>
+      <c r="M11">
+        <v>675000</v>
+      </c>
+      <c r="N11">
+        <v>585000</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="I12" s="1">
+      <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12">
         <v>0.8625954198473282</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12">
         <v>0.3096926713947991</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12">
         <v>655000</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12">
         <v>565000</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="I13" s="1">
+      <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="2">
-        <v>0.881578947368421</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0.3370288248337029</v>
-      </c>
-      <c r="M13" s="1">
-        <v>760000</v>
-      </c>
-      <c r="N13" s="1">
-        <v>670000</v>
+      <c r="K13">
+        <v>0.8782051282051282</v>
+      </c>
+      <c r="L13">
+        <v>0.3458980044345898</v>
+      </c>
+      <c r="M13">
+        <v>780000</v>
+      </c>
+      <c r="N13">
+        <v>685000</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="I14" s="1">
+      <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="2">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0.2923433874709977</v>
-      </c>
-      <c r="M14" s="1">
-        <v>630000</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="K14">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="L14">
+        <v>0.2993039443155452</v>
+      </c>
+      <c r="M14">
+        <v>645000</v>
+      </c>
+      <c r="N14">
         <v>510000</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="I15" s="1">
+      <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="2">
-        <v>0.8222222222222222</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0.2954048140043763</v>
-      </c>
-      <c r="M15" s="1">
-        <v>675000</v>
-      </c>
-      <c r="N15" s="1">
-        <v>555000</v>
+      <c r="K15">
+        <v>0.8270676691729323</v>
+      </c>
+      <c r="L15">
+        <v>0.2910284463894967</v>
+      </c>
+      <c r="M15">
+        <v>665000</v>
+      </c>
+      <c r="N15">
+        <v>550000</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="I16" s="1">
+      <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="2">
-        <v>0.8706896551724138</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0.2516268980477224</v>
-      </c>
-      <c r="M16" s="1">
-        <v>580000</v>
-      </c>
-      <c r="N16" s="1">
-        <v>505000</v>
+      <c r="K16">
+        <v>0.8869565217391304</v>
+      </c>
+      <c r="L16">
+        <v>0.2494577006507592</v>
+      </c>
+      <c r="M16">
+        <v>575000</v>
+      </c>
+      <c r="N16">
+        <v>510000</v>
       </c>
     </row>
     <row r="17" spans="9:14">
-      <c r="I17" s="1">
+      <c r="I17">
         <v>1</v>
       </c>
       <c r="J17" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="2">
-        <v>0.3269230769230769</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0.3959390862944163</v>
-      </c>
-      <c r="M17" s="1">
-        <v>780000</v>
-      </c>
-      <c r="N17" s="1">
-        <v>255000</v>
+      <c r="K17">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L17">
+        <v>0.4035532994923858</v>
+      </c>
+      <c r="M17">
+        <v>795000</v>
+      </c>
+      <c r="N17">
+        <v>265000</v>
       </c>
     </row>
     <row r="18" spans="9:14">
-      <c r="I18" s="1">
+      <c r="I18">
         <v>1</v>
       </c>
       <c r="J18" t="s">
         <v>9</v>
       </c>
-      <c r="K18" s="2">
-        <v>0.4864864864864865</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0.4195011337868481</v>
-      </c>
-      <c r="M18" s="1">
-        <v>925000</v>
-      </c>
-      <c r="N18" s="1">
+      <c r="K18">
+        <v>0.4787234042553192</v>
+      </c>
+      <c r="L18">
+        <v>0.4263038548752834</v>
+      </c>
+      <c r="M18">
+        <v>940000</v>
+      </c>
+      <c r="N18">
         <v>450000</v>
       </c>
     </row>
     <row r="19" spans="9:14">
-      <c r="I19" s="1">
+      <c r="I19">
         <v>1</v>
       </c>
       <c r="J19" t="s">
         <v>10</v>
       </c>
-      <c r="K19" s="2">
-        <v>0.4943181818181818</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="M19" s="1">
-        <v>880000</v>
-      </c>
-      <c r="N19" s="1">
-        <v>435000</v>
+      <c r="K19">
+        <v>0.4855491329479769</v>
+      </c>
+      <c r="L19">
+        <v>0.400462962962963</v>
+      </c>
+      <c r="M19">
+        <v>865000</v>
+      </c>
+      <c r="N19">
+        <v>420000</v>
       </c>
     </row>
     <row r="20" spans="9:14">
-      <c r="I20" s="1">
+      <c r="I20">
         <v>1</v>
       </c>
       <c r="J20" t="s">
         <v>11</v>
       </c>
-      <c r="K20" s="2">
-        <v>0.4539473684210527</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0.3326039387308534</v>
-      </c>
-      <c r="M20" s="1">
-        <v>760000</v>
-      </c>
-      <c r="N20" s="1">
-        <v>345000</v>
+      <c r="K20">
+        <v>0.4840764331210191</v>
+      </c>
+      <c r="L20">
+        <v>0.3435448577680525</v>
+      </c>
+      <c r="M20">
+        <v>785000</v>
+      </c>
+      <c r="N20">
+        <v>380000</v>
       </c>
     </row>
     <row r="21" spans="9:14">
-      <c r="I21" s="1">
+      <c r="I21">
         <v>1</v>
       </c>
       <c r="J21" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="2">
-        <v>0.5135135135135135</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0.3363636363636364</v>
-      </c>
-      <c r="M21" s="1">
-        <v>740000</v>
-      </c>
-      <c r="N21" s="1">
-        <v>380000</v>
+      <c r="K21">
+        <v>0.5034013605442177</v>
+      </c>
+      <c r="L21">
+        <v>0.3340909090909091</v>
+      </c>
+      <c r="M21">
+        <v>735000</v>
+      </c>
+      <c r="N21">
+        <v>370000</v>
       </c>
     </row>
     <row r="22" spans="9:14">
-      <c r="I22" s="1">
+      <c r="I22">
         <v>1</v>
       </c>
       <c r="J22" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="2">
-        <v>0.4802631578947368</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0.3734643734643734</v>
-      </c>
-      <c r="M22" s="1">
-        <v>760000</v>
-      </c>
-      <c r="N22" s="1">
-        <v>365000</v>
+      <c r="K22">
+        <v>0.4794520547945205</v>
+      </c>
+      <c r="L22">
+        <v>0.3587223587223587</v>
+      </c>
+      <c r="M22">
+        <v>730000</v>
+      </c>
+      <c r="N22">
+        <v>350000</v>
       </c>
     </row>
     <row r="23" spans="9:14">
-      <c r="I23" s="1">
+      <c r="I23">
         <v>1</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="2">
-        <v>0.4901960784313725</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0.3485193621867881</v>
-      </c>
-      <c r="M23" s="1">
-        <v>765000</v>
-      </c>
-      <c r="N23" s="1">
-        <v>375000</v>
+      <c r="K23">
+        <v>0.5033112582781457</v>
+      </c>
+      <c r="L23">
+        <v>0.3439635535307517</v>
+      </c>
+      <c r="M23">
+        <v>755000</v>
+      </c>
+      <c r="N23">
+        <v>380000</v>
       </c>
     </row>
     <row r="24" spans="9:14">
-      <c r="I24" s="1">
+      <c r="I24">
         <v>1</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
-      <c r="K24" s="2">
-        <v>0.4796747967479675</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0.2992700729927008</v>
-      </c>
-      <c r="M24" s="1">
-        <v>615000</v>
-      </c>
-      <c r="N24" s="1">
-        <v>295000</v>
+      <c r="K24">
+        <v>0.4803149606299212</v>
+      </c>
+      <c r="L24">
+        <v>0.3090024330900243</v>
+      </c>
+      <c r="M24">
+        <v>635000</v>
+      </c>
+      <c r="N24">
+        <v>305000</v>
       </c>
     </row>
     <row r="25" spans="9:14">
-      <c r="I25" s="1">
+      <c r="I25">
         <v>1</v>
       </c>
       <c r="J25" t="s">
         <v>16</v>
       </c>
-      <c r="K25" s="2">
-        <v>0.456</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0.2955082742316785</v>
-      </c>
-      <c r="M25" s="1">
-        <v>625000</v>
-      </c>
-      <c r="N25" s="1">
+      <c r="K25">
+        <v>0.4634146341463415</v>
+      </c>
+      <c r="L25">
+        <v>0.2907801418439716</v>
+      </c>
+      <c r="M25">
+        <v>615000</v>
+      </c>
+      <c r="N25">
         <v>285000</v>
       </c>
     </row>
     <row r="26" spans="9:14">
-      <c r="I26" s="1">
+      <c r="I26">
         <v>1</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
       </c>
-      <c r="K26" s="2">
-        <v>0.5528455284552846</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="M26" s="1">
-        <v>615000</v>
-      </c>
-      <c r="N26" s="1">
-        <v>340000</v>
+      <c r="K26">
+        <v>0.5508474576271186</v>
+      </c>
+      <c r="L26">
+        <v>0.2616407982261641</v>
+      </c>
+      <c r="M26">
+        <v>590000</v>
+      </c>
+      <c r="N26">
+        <v>325000</v>
       </c>
     </row>
     <row r="27" spans="9:14">
-      <c r="I27" s="1">
+      <c r="I27">
         <v>1</v>
       </c>
       <c r="J27" t="s">
         <v>18</v>
       </c>
-      <c r="K27" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0.2645011600928074</v>
-      </c>
-      <c r="M27" s="1">
-        <v>570000</v>
-      </c>
-      <c r="N27" s="1">
+      <c r="K27">
+        <v>0.504424778761062</v>
+      </c>
+      <c r="L27">
+        <v>0.2621809744779582</v>
+      </c>
+      <c r="M27">
+        <v>565000</v>
+      </c>
+      <c r="N27">
         <v>285000</v>
       </c>
     </row>
     <row r="28" spans="9:14">
-      <c r="I28" s="1">
+      <c r="I28">
         <v>1</v>
       </c>
       <c r="J28" t="s">
         <v>19</v>
       </c>
-      <c r="K28" s="2">
-        <v>0.5597014925373134</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0.2932166301969366</v>
-      </c>
-      <c r="M28" s="1">
-        <v>670000</v>
-      </c>
-      <c r="N28" s="1">
-        <v>375000</v>
+      <c r="K28">
+        <v>0.5507246376811594</v>
+      </c>
+      <c r="L28">
+        <v>0.3019693654266958</v>
+      </c>
+      <c r="M28">
+        <v>690000</v>
+      </c>
+      <c r="N28">
+        <v>380000</v>
       </c>
     </row>
     <row r="29" spans="9:14">
-      <c r="I29" s="1">
+      <c r="I29">
         <v>1</v>
       </c>
       <c r="J29" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="2">
-        <v>0.5357142857142857</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0.3036876355748373</v>
-      </c>
-      <c r="M29" s="1">
-        <v>700000</v>
-      </c>
-      <c r="N29" s="1">
-        <v>375000</v>
+      <c r="K29">
+        <v>0.524822695035461</v>
+      </c>
+      <c r="L29">
+        <v>0.3058568329718004</v>
+      </c>
+      <c r="M29">
+        <v>705000</v>
+      </c>
+      <c r="N29">
+        <v>370000</v>
       </c>
     </row>
     <row r="30" spans="9:14">
-      <c r="I30" s="1">
+      <c r="I30">
         <v>2</v>
       </c>
       <c r="J30" t="s">
         <v>8</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="1">
-        <v>0.1421319796954315</v>
-      </c>
-      <c r="M30" s="1">
-        <v>280000</v>
-      </c>
-      <c r="N30" s="1">
+      <c r="L30">
+        <v>0.1472081218274112</v>
+      </c>
+      <c r="M30">
+        <v>290000</v>
+      </c>
+      <c r="N30">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="9:14">
-      <c r="I31" s="1">
+      <c r="I31">
         <v>2</v>
       </c>
       <c r="J31" t="s">
         <v>9</v>
       </c>
-      <c r="K31" s="2">
-        <v>0.07954545454545454</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0.199546485260771</v>
-      </c>
-      <c r="M31" s="1">
-        <v>440000</v>
-      </c>
-      <c r="N31" s="1">
+      <c r="K31">
+        <v>0.08139534883720931</v>
+      </c>
+      <c r="L31">
+        <v>0.1950113378684807</v>
+      </c>
+      <c r="M31">
+        <v>430000</v>
+      </c>
+      <c r="N31">
         <v>35000</v>
       </c>
     </row>
     <row r="32" spans="9:14">
-      <c r="I32" s="1">
+      <c r="I32">
         <v>2</v>
       </c>
       <c r="J32" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="2">
-        <v>0.09174311926605505</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0.2523148148148148</v>
-      </c>
-      <c r="M32" s="1">
-        <v>545000</v>
-      </c>
-      <c r="N32" s="1">
-        <v>50000</v>
+      <c r="K32">
+        <v>0.1</v>
+      </c>
+      <c r="L32">
+        <v>0.2546296296296297</v>
+      </c>
+      <c r="M32">
+        <v>550000</v>
+      </c>
+      <c r="N32">
+        <v>55000</v>
       </c>
     </row>
     <row r="33" spans="9:14">
-      <c r="I33" s="1">
+      <c r="I33">
         <v>2</v>
       </c>
       <c r="J33" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="2">
-        <v>0.1458333333333333</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="K33">
+        <v>0.1319444444444444</v>
+      </c>
+      <c r="L33">
         <v>0.3150984682713348</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M33">
         <v>720000</v>
       </c>
-      <c r="N33" s="1">
-        <v>105000</v>
+      <c r="N33">
+        <v>95000</v>
       </c>
     </row>
     <row r="34" spans="9:14">
-      <c r="I34" s="1">
+      <c r="I34">
         <v>2</v>
       </c>
       <c r="J34" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="2">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0.3022727272727272</v>
-      </c>
-      <c r="M34" s="1">
-        <v>665000</v>
-      </c>
-      <c r="N34" s="1">
+      <c r="K34">
+        <v>0.1060606060606061</v>
+      </c>
+      <c r="L34">
+        <v>0.3</v>
+      </c>
+      <c r="M34">
+        <v>660000</v>
+      </c>
+      <c r="N34">
         <v>70000</v>
       </c>
     </row>
     <row r="35" spans="9:14">
-      <c r="I35" s="1">
+      <c r="I35">
         <v>2</v>
       </c>
       <c r="J35" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="2">
-        <v>0.1395348837209302</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0.316953316953317</v>
-      </c>
-      <c r="M35" s="1">
-        <v>645000</v>
-      </c>
-      <c r="N35" s="1">
+      <c r="K35">
+        <v>0.1384615384615385</v>
+      </c>
+      <c r="L35">
+        <v>0.3194103194103194</v>
+      </c>
+      <c r="M35">
+        <v>650000</v>
+      </c>
+      <c r="N35">
         <v>90000</v>
       </c>
     </row>
     <row r="36" spans="9:14">
-      <c r="I36" s="1">
+      <c r="I36">
         <v>2</v>
       </c>
       <c r="J36" t="s">
         <v>14</v>
       </c>
-      <c r="K36" s="2">
-        <v>0.1458333333333333</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0.3280182232346242</v>
-      </c>
-      <c r="M36" s="1">
-        <v>720000</v>
-      </c>
-      <c r="N36" s="1">
+      <c r="K36">
+        <v>0.1438356164383562</v>
+      </c>
+      <c r="L36">
+        <v>0.3325740318906606</v>
+      </c>
+      <c r="M36">
+        <v>730000</v>
+      </c>
+      <c r="N36">
         <v>105000</v>
       </c>
     </row>
     <row r="37" spans="9:14">
-      <c r="I37" s="1">
+      <c r="I37">
         <v>2</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
-      <c r="K37" s="2">
-        <v>0.1059602649006623</v>
-      </c>
-      <c r="L37" s="1">
-        <v>0.3673965936739659</v>
-      </c>
-      <c r="M37" s="1">
-        <v>755000</v>
-      </c>
-      <c r="N37" s="1">
+      <c r="K37">
+        <v>0.1073825503355705</v>
+      </c>
+      <c r="L37">
+        <v>0.3625304136253041</v>
+      </c>
+      <c r="M37">
+        <v>745000</v>
+      </c>
+      <c r="N37">
         <v>80000</v>
       </c>
     </row>
     <row r="38" spans="9:14">
-      <c r="I38" s="1">
+      <c r="I38">
         <v>2</v>
       </c>
       <c r="J38" t="s">
         <v>16</v>
       </c>
-      <c r="K38" s="2">
-        <v>0.09580838323353294</v>
-      </c>
-      <c r="L38" s="1">
-        <v>0.3947990543735225</v>
-      </c>
-      <c r="M38" s="1">
-        <v>835000</v>
-      </c>
-      <c r="N38" s="1">
+      <c r="K38">
+        <v>0.09467455621301775</v>
+      </c>
+      <c r="L38">
+        <v>0.3995271867612293</v>
+      </c>
+      <c r="M38">
+        <v>845000</v>
+      </c>
+      <c r="N38">
         <v>80000</v>
       </c>
     </row>
     <row r="39" spans="9:14">
-      <c r="I39" s="1">
+      <c r="I39">
         <v>2</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
       </c>
-      <c r="K39" s="2">
-        <v>0.09659090909090909</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0.3902439024390244</v>
-      </c>
-      <c r="M39" s="1">
-        <v>880000</v>
-      </c>
-      <c r="N39" s="1">
+      <c r="K39">
+        <v>0.096045197740113</v>
+      </c>
+      <c r="L39">
+        <v>0.3924611973392461</v>
+      </c>
+      <c r="M39">
+        <v>885000</v>
+      </c>
+      <c r="N39">
         <v>85000</v>
       </c>
     </row>
     <row r="40" spans="9:14">
-      <c r="I40" s="1">
+      <c r="I40">
         <v>2</v>
       </c>
       <c r="J40" t="s">
         <v>18</v>
       </c>
-      <c r="K40" s="2">
-        <v>0.1047120418848168</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0.4431554524361949</v>
-      </c>
-      <c r="M40" s="1">
-        <v>955000</v>
-      </c>
-      <c r="N40" s="1">
+      <c r="K40">
+        <v>0.1058201058201058</v>
+      </c>
+      <c r="L40">
+        <v>0.4385150812064965</v>
+      </c>
+      <c r="M40">
+        <v>945000</v>
+      </c>
+      <c r="N40">
         <v>100000</v>
       </c>
     </row>
     <row r="41" spans="9:14">
-      <c r="I41" s="1">
+      <c r="I41">
         <v>2</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
       </c>
-      <c r="K41" s="2">
-        <v>0.1170212765957447</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0.4113785557986871</v>
-      </c>
-      <c r="M41" s="1">
-        <v>940000</v>
-      </c>
-      <c r="N41" s="1">
+      <c r="K41">
+        <v>0.1182795698924731</v>
+      </c>
+      <c r="L41">
+        <v>0.4070021881838075</v>
+      </c>
+      <c r="M41">
+        <v>930000</v>
+      </c>
+      <c r="N41">
         <v>110000</v>
       </c>
     </row>
     <row r="42" spans="9:14">
-      <c r="I42" s="1">
+      <c r="I42">
         <v>2</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="2">
+      <c r="K42">
         <v>0.07804878048780488</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L42">
         <v>0.4446854663774403</v>
       </c>
-      <c r="M42" s="1">
+      <c r="M42">
         <v>1025000</v>
       </c>
-      <c r="N42" s="1">
+      <c r="N42">
         <v>80000</v>
       </c>
     </row>

--- a/outputs/pd_css_cross/Segments3_report.xlsx
+++ b/outputs/pd_css_cross/Segments3_report.xlsx
@@ -249,43 +249,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.8248587570621468</c:v>
+                  <c:v>0.941747572815534</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9101796407185628</c:v>
+                  <c:v>0.9557522123893806</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9060402684563759</c:v>
+                  <c:v>0.9603960396039604</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9358974358974359</c:v>
+                  <c:v>0.9734513274336283</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9192546583850931</c:v>
+                  <c:v>0.9607843137254902</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8931297709923665</c:v>
+                  <c:v>0.9325842696629213</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8802816901408451</c:v>
+                  <c:v>0.9148936170212766</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0.8762886597938144</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.898876404494382</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9175257731958762</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.8666666666666667</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.8625954198473282</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.8782051282051282</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.7906976744186046</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8270676691729323</c:v>
+                  <c:v>0.8620689655172413</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8869565217391304</c:v>
+                  <c:v>0.9605263157894737</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -363,43 +363,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3333333333333333</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4787234042553192</c:v>
+                  <c:v>0.7339449541284404</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4855491329479769</c:v>
+                  <c:v>0.7195121951219512</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4840764331210191</c:v>
+                  <c:v>0.7875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5034013605442177</c:v>
+                  <c:v>0.7171717171717171</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4794520547945205</c:v>
+                  <c:v>0.7272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5033112582781457</c:v>
+                  <c:v>0.7394957983193278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4803149606299212</c:v>
+                  <c:v>0.7692307692307693</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4634146341463415</c:v>
+                  <c:v>0.7529411764705882</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5508474576271186</c:v>
+                  <c:v>0.72</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.504424778761062</c:v>
+                  <c:v>0.6404494382022472</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5507246376811594</c:v>
+                  <c:v>0.7192982456140351</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.524822695035461</c:v>
+                  <c:v>0.635593220338983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -477,43 +477,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.04285714285714286</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.08139534883720931</c:v>
+                  <c:v>0.1022727272727273</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0.07954545454545454</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.07920792079207921</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1319444444444444</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1060606060606061</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1384615384615385</c:v>
+                  <c:v>0.1739130434782609</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1438356164383562</c:v>
+                  <c:v>0.0379746835443038</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1073825503355705</c:v>
+                  <c:v>0.07526881720430108</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.09467455621301775</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.096045197740113</c:v>
+                  <c:v>0.1071428571428571</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1058201058201058</c:v>
+                  <c:v>0.1025641025641026</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1182795698924731</c:v>
+                  <c:v>0.07407407407407407</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.07804878048780488</c:v>
+                  <c:v>0.04464285714285714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -691,43 +691,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.4492385786802031</c:v>
+                  <c:v>0.3772893772893773</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3786848072562358</c:v>
+                  <c:v>0.3645161290322581</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3449074074074074</c:v>
+                  <c:v>0.3726937269372694</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3413566739606127</c:v>
+                  <c:v>0.3843537414965986</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3659090909090909</c:v>
+                  <c:v>0.3505154639175257</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3218673218673219</c:v>
+                  <c:v>0.3449612403100775</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3234624145785877</c:v>
+                  <c:v>0.3219178082191781</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3284671532846715</c:v>
+                  <c:v>0.3619402985074627</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3096926713947991</c:v>
+                  <c:v>0.3248175182481752</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3458980044345898</c:v>
+                  <c:v>0.313915857605178</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2993039443155452</c:v>
+                  <c:v>0.3040540540540541</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2910284463894967</c:v>
+                  <c:v>0.2815533980582524</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2494577006507592</c:v>
+                  <c:v>0.2483660130718954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -805,43 +805,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.4035532994923858</c:v>
+                  <c:v>0.3663003663003663</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4263038548752834</c:v>
+                  <c:v>0.3516129032258065</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.400462962962963</c:v>
+                  <c:v>0.3025830258302583</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3435448577680525</c:v>
+                  <c:v>0.272108843537415</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3340909090909091</c:v>
+                  <c:v>0.3402061855670103</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3587223587223587</c:v>
+                  <c:v>0.2984496124031008</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3439635535307517</c:v>
+                  <c:v>0.4075342465753425</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3090024330900243</c:v>
+                  <c:v>0.291044776119403</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2907801418439716</c:v>
+                  <c:v>0.3102189781021898</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2616407982261641</c:v>
+                  <c:v>0.3236245954692556</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2621809744779582</c:v>
+                  <c:v>0.3006756756756757</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3019693654266958</c:v>
+                  <c:v>0.3689320388349515</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3058568329718004</c:v>
+                  <c:v>0.3856209150326798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -919,43 +919,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1472081218274112</c:v>
+                  <c:v>0.2564102564102564</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1950113378684807</c:v>
+                  <c:v>0.2838709677419355</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2546296296296297</c:v>
+                  <c:v>0.3247232472324723</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3150984682713348</c:v>
+                  <c:v>0.3435374149659864</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3</c:v>
+                  <c:v>0.3092783505154639</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3194103194103194</c:v>
+                  <c:v>0.3565891472868217</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3325740318906606</c:v>
+                  <c:v>0.2705479452054795</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3625304136253041</c:v>
+                  <c:v>0.3470149253731343</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3995271867612293</c:v>
+                  <c:v>0.364963503649635</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3924611973392461</c:v>
+                  <c:v>0.3624595469255664</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4385150812064965</c:v>
+                  <c:v>0.3952702702702703</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4070021881838075</c:v>
+                  <c:v>0.3495145631067961</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4446854663774403</c:v>
+                  <c:v>0.3660130718954248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1133,43 +1133,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.8248587570621468</c:v>
+                  <c:v>0.941747572815534</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9101796407185628</c:v>
+                  <c:v>0.9557522123893806</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9060402684563759</c:v>
+                  <c:v>0.9603960396039604</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9358974358974359</c:v>
+                  <c:v>0.9734513274336283</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9192546583850931</c:v>
+                  <c:v>0.9607843137254902</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8931297709923665</c:v>
+                  <c:v>0.9325842696629213</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8802816901408451</c:v>
+                  <c:v>0.9148936170212766</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0.8762886597938144</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.898876404494382</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9175257731958762</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0.8666666666666667</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.8625954198473282</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.8782051282051282</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.7906976744186046</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8270676691729323</c:v>
+                  <c:v>0.8620689655172413</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8869565217391304</c:v>
+                  <c:v>0.9605263157894737</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1247,43 +1247,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3333333333333333</c:v>
+                  <c:v>0.54</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4787234042553192</c:v>
+                  <c:v>0.7339449541284404</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4855491329479769</c:v>
+                  <c:v>0.7195121951219512</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4840764331210191</c:v>
+                  <c:v>0.7875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5034013605442177</c:v>
+                  <c:v>0.7171717171717171</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4794520547945205</c:v>
+                  <c:v>0.7272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5033112582781457</c:v>
+                  <c:v>0.7394957983193278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4803149606299212</c:v>
+                  <c:v>0.7692307692307693</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4634146341463415</c:v>
+                  <c:v>0.7529411764705882</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5508474576271186</c:v>
+                  <c:v>0.72</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.504424778761062</c:v>
+                  <c:v>0.6404494382022472</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5507246376811594</c:v>
+                  <c:v>0.7192982456140351</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.524822695035461</c:v>
+                  <c:v>0.635593220338983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1361,43 +1361,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.04285714285714286</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.08139534883720931</c:v>
+                  <c:v>0.1022727272727273</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0.07954545454545454</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.07920792079207921</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1319444444444444</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1060606060606061</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1384615384615385</c:v>
+                  <c:v>0.1739130434782609</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1438356164383562</c:v>
+                  <c:v>0.0379746835443038</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1073825503355705</c:v>
+                  <c:v>0.07526881720430108</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.09467455621301775</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.096045197740113</c:v>
+                  <c:v>0.1071428571428571</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1058201058201058</c:v>
+                  <c:v>0.1025641025641026</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1182795698924731</c:v>
+                  <c:v>0.07407407407407407</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.07804878048780488</c:v>
+                  <c:v>0.04464285714285714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1575,43 +1575,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.4492385786802031</c:v>
+                  <c:v>0.3772893772893773</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3786848072562358</c:v>
+                  <c:v>0.3645161290322581</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3449074074074074</c:v>
+                  <c:v>0.3726937269372694</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3413566739606127</c:v>
+                  <c:v>0.3843537414965986</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3659090909090909</c:v>
+                  <c:v>0.3505154639175257</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3218673218673219</c:v>
+                  <c:v>0.3449612403100775</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3234624145785877</c:v>
+                  <c:v>0.3219178082191781</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3284671532846715</c:v>
+                  <c:v>0.3619402985074627</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3096926713947991</c:v>
+                  <c:v>0.3248175182481752</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3458980044345898</c:v>
+                  <c:v>0.313915857605178</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2993039443155452</c:v>
+                  <c:v>0.3040540540540541</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2910284463894967</c:v>
+                  <c:v>0.2815533980582524</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2494577006507592</c:v>
+                  <c:v>0.2483660130718954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1689,43 +1689,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.4035532994923858</c:v>
+                  <c:v>0.3663003663003663</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.4263038548752834</c:v>
+                  <c:v>0.3516129032258065</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.400462962962963</c:v>
+                  <c:v>0.3025830258302583</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3435448577680525</c:v>
+                  <c:v>0.272108843537415</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3340909090909091</c:v>
+                  <c:v>0.3402061855670103</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3587223587223587</c:v>
+                  <c:v>0.2984496124031008</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3439635535307517</c:v>
+                  <c:v>0.4075342465753425</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3090024330900243</c:v>
+                  <c:v>0.291044776119403</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2907801418439716</c:v>
+                  <c:v>0.3102189781021898</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2616407982261641</c:v>
+                  <c:v>0.3236245954692556</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2621809744779582</c:v>
+                  <c:v>0.3006756756756757</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3019693654266958</c:v>
+                  <c:v>0.3689320388349515</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3058568329718004</c:v>
+                  <c:v>0.3856209150326798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1803,43 +1803,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.1472081218274112</c:v>
+                  <c:v>0.2564102564102564</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1950113378684807</c:v>
+                  <c:v>0.2838709677419355</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2546296296296297</c:v>
+                  <c:v>0.3247232472324723</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3150984682713348</c:v>
+                  <c:v>0.3435374149659864</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3</c:v>
+                  <c:v>0.3092783505154639</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3194103194103194</c:v>
+                  <c:v>0.3565891472868217</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3325740318906606</c:v>
+                  <c:v>0.2705479452054795</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3625304136253041</c:v>
+                  <c:v>0.3470149253731343</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3995271867612293</c:v>
+                  <c:v>0.364963503649635</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3924611973392461</c:v>
+                  <c:v>0.3624595469255664</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4385150812064965</c:v>
+                  <c:v>0.3952702702702703</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4070021881838075</c:v>
+                  <c:v>0.3495145631067961</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4446854663774403</c:v>
+                  <c:v>0.3660130718954248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2389,22 +2389,22 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>0.9545565931879846</v>
+        <v>1.852583220312426</v>
       </c>
       <c r="C4">
-        <v>8.107875986233042</v>
+        <v>6.642385548595935</v>
       </c>
       <c r="D4">
-        <v>0.8767268862911796</v>
+        <v>0.9264588329336531</v>
       </c>
       <c r="E4">
-        <v>0.3334514528703048</v>
+        <v>0.3335110637163423</v>
       </c>
       <c r="F4">
-        <v>1882</v>
+        <v>1251</v>
       </c>
       <c r="G4">
-        <v>1650</v>
+        <v>1159</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2413,16 +2413,16 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>0.8248587570621468</v>
+        <v>0.941747572815534</v>
       </c>
       <c r="L4">
-        <v>0.4492385786802031</v>
+        <v>0.3772893772893773</v>
       </c>
       <c r="M4">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="N4">
-        <v>146</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2430,22 +2430,22 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>-1.0100583376388</v>
+        <v>-0.340458278724456</v>
       </c>
       <c r="C5">
-        <v>0.9491980724600928</v>
+        <v>1.852108499754602</v>
       </c>
       <c r="D5">
-        <v>0.4853801169590643</v>
+        <v>0.7048</v>
       </c>
       <c r="E5">
-        <v>0.3332742735648476</v>
+        <v>0.3332444681418288</v>
       </c>
       <c r="F5">
-        <v>1881</v>
+        <v>1250</v>
       </c>
       <c r="G5">
-        <v>913</v>
+        <v>881</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2454,16 +2454,16 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>0.9101796407185628</v>
+        <v>0.9557522123893806</v>
       </c>
       <c r="L5">
-        <v>0.3786848072562358</v>
+        <v>0.3645161290322581</v>
       </c>
       <c r="M5">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="N5">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2471,22 +2471,22 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>-10.75813788412185</v>
+        <v>-12.96610599108593</v>
       </c>
       <c r="C6">
-        <v>-1.010537872244683</v>
+        <v>-0.3430929032834529</v>
       </c>
       <c r="D6">
-        <v>0.1047315257841574</v>
+        <v>0.0832</v>
       </c>
       <c r="E6">
-        <v>0.3332742735648476</v>
+        <v>0.3332444681418288</v>
       </c>
       <c r="F6">
-        <v>1881</v>
+        <v>1250</v>
       </c>
       <c r="G6">
-        <v>197</v>
+        <v>104</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2495,16 +2495,16 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>0.9060402684563759</v>
+        <v>0.9603960396039604</v>
       </c>
       <c r="L6">
-        <v>0.3449074074074074</v>
+        <v>0.3726937269372694</v>
       </c>
       <c r="M6">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="N6">
-        <v>135</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2515,16 +2515,16 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>0.9358974358974359</v>
+        <v>0.9734513274336283</v>
       </c>
       <c r="L7">
-        <v>0.3413566739606127</v>
+        <v>0.3843537414965986</v>
       </c>
       <c r="M7">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="N7">
-        <v>146</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2535,16 +2535,16 @@
         <v>12</v>
       </c>
       <c r="K8">
-        <v>0.9192546583850931</v>
+        <v>0.9607843137254902</v>
       </c>
       <c r="L8">
-        <v>0.3659090909090909</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M8">
-        <v>161</v>
+        <v>102</v>
       </c>
       <c r="N8">
-        <v>148</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2555,16 +2555,16 @@
         <v>13</v>
       </c>
       <c r="K9">
-        <v>0.8931297709923665</v>
+        <v>0.9325842696629213</v>
       </c>
       <c r="L9">
-        <v>0.3218673218673219</v>
+        <v>0.3449612403100775</v>
       </c>
       <c r="M9">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="N9">
-        <v>117</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2575,16 +2575,16 @@
         <v>14</v>
       </c>
       <c r="K10">
-        <v>0.8802816901408451</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="L10">
-        <v>0.3234624145785877</v>
+        <v>0.3219178082191781</v>
       </c>
       <c r="M10">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="N10">
-        <v>125</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2595,16 +2595,16 @@
         <v>15</v>
       </c>
       <c r="K11">
-        <v>0.8666666666666667</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="L11">
-        <v>0.3284671532846715</v>
+        <v>0.3619402985074627</v>
       </c>
       <c r="M11">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="N11">
-        <v>117</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2615,16 +2615,16 @@
         <v>16</v>
       </c>
       <c r="K12">
-        <v>0.8625954198473282</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="L12">
-        <v>0.3096926713947991</v>
+        <v>0.3248175182481752</v>
       </c>
       <c r="M12">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="N12">
-        <v>113</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2635,16 +2635,16 @@
         <v>17</v>
       </c>
       <c r="K13">
-        <v>0.8782051282051282</v>
+        <v>0.9175257731958762</v>
       </c>
       <c r="L13">
-        <v>0.3458980044345898</v>
+        <v>0.313915857605178</v>
       </c>
       <c r="M13">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="N13">
-        <v>137</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -2655,16 +2655,16 @@
         <v>18</v>
       </c>
       <c r="K14">
-        <v>0.7906976744186046</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L14">
-        <v>0.2993039443155452</v>
+        <v>0.3040540540540541</v>
       </c>
       <c r="M14">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="N14">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2675,16 +2675,16 @@
         <v>19</v>
       </c>
       <c r="K15">
-        <v>0.8270676691729323</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="L15">
-        <v>0.2910284463894967</v>
+        <v>0.2815533980582524</v>
       </c>
       <c r="M15">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="N15">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2695,16 +2695,16 @@
         <v>20</v>
       </c>
       <c r="K16">
-        <v>0.8869565217391304</v>
+        <v>0.9605263157894737</v>
       </c>
       <c r="L16">
-        <v>0.2494577006507592</v>
+        <v>0.2483660130718954</v>
       </c>
       <c r="M16">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="N16">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="9:14">
@@ -2715,16 +2715,16 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>0.3333333333333333</v>
+        <v>0.54</v>
       </c>
       <c r="L17">
-        <v>0.4035532994923858</v>
+        <v>0.3663003663003663</v>
       </c>
       <c r="M17">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="9:14">
@@ -2735,16 +2735,16 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>0.4787234042553192</v>
+        <v>0.7339449541284404</v>
       </c>
       <c r="L18">
-        <v>0.4263038548752834</v>
+        <v>0.3516129032258065</v>
       </c>
       <c r="M18">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="N18">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="9:14">
@@ -2755,16 +2755,16 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>0.4855491329479769</v>
+        <v>0.7195121951219512</v>
       </c>
       <c r="L19">
-        <v>0.400462962962963</v>
+        <v>0.3025830258302583</v>
       </c>
       <c r="M19">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="N19">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="9:14">
@@ -2775,16 +2775,16 @@
         <v>11</v>
       </c>
       <c r="K20">
-        <v>0.4840764331210191</v>
+        <v>0.7875</v>
       </c>
       <c r="L20">
-        <v>0.3435448577680525</v>
+        <v>0.272108843537415</v>
       </c>
       <c r="M20">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="N20">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="9:14">
@@ -2795,16 +2795,16 @@
         <v>12</v>
       </c>
       <c r="K21">
-        <v>0.5034013605442177</v>
+        <v>0.7171717171717171</v>
       </c>
       <c r="L21">
-        <v>0.3340909090909091</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="M21">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="N21">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="9:14">
@@ -2815,16 +2815,16 @@
         <v>13</v>
       </c>
       <c r="K22">
-        <v>0.4794520547945205</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L22">
-        <v>0.3587223587223587</v>
+        <v>0.2984496124031008</v>
       </c>
       <c r="M22">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="N22">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="9:14">
@@ -2835,16 +2835,16 @@
         <v>14</v>
       </c>
       <c r="K23">
-        <v>0.5033112582781457</v>
+        <v>0.7394957983193278</v>
       </c>
       <c r="L23">
-        <v>0.3439635535307517</v>
+        <v>0.4075342465753425</v>
       </c>
       <c r="M23">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="N23">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="9:14">
@@ -2855,16 +2855,16 @@
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.4803149606299212</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L24">
-        <v>0.3090024330900243</v>
+        <v>0.291044776119403</v>
       </c>
       <c r="M24">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="N24">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="9:14">
@@ -2875,16 +2875,16 @@
         <v>16</v>
       </c>
       <c r="K25">
-        <v>0.4634146341463415</v>
+        <v>0.7529411764705882</v>
       </c>
       <c r="L25">
-        <v>0.2907801418439716</v>
+        <v>0.3102189781021898</v>
       </c>
       <c r="M25">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="N25">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="9:14">
@@ -2895,16 +2895,16 @@
         <v>17</v>
       </c>
       <c r="K26">
-        <v>0.5508474576271186</v>
+        <v>0.72</v>
       </c>
       <c r="L26">
-        <v>0.2616407982261641</v>
+        <v>0.3236245954692556</v>
       </c>
       <c r="M26">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="9:14">
@@ -2915,13 +2915,13 @@
         <v>18</v>
       </c>
       <c r="K27">
-        <v>0.504424778761062</v>
+        <v>0.6404494382022472</v>
       </c>
       <c r="L27">
-        <v>0.2621809744779582</v>
+        <v>0.3006756756756757</v>
       </c>
       <c r="M27">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="N27">
         <v>57</v>
@@ -2935,16 +2935,16 @@
         <v>19</v>
       </c>
       <c r="K28">
-        <v>0.5507246376811594</v>
+        <v>0.7192982456140351</v>
       </c>
       <c r="L28">
-        <v>0.3019693654266958</v>
+        <v>0.3689320388349515</v>
       </c>
       <c r="M28">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="N28">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="9:14">
@@ -2955,16 +2955,16 @@
         <v>20</v>
       </c>
       <c r="K29">
-        <v>0.524822695035461</v>
+        <v>0.635593220338983</v>
       </c>
       <c r="L29">
-        <v>0.3058568329718004</v>
+        <v>0.3856209150326798</v>
       </c>
       <c r="M29">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="N29">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="9:14">
@@ -2975,16 +2975,16 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="L30">
-        <v>0.1472081218274112</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="M30">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="9:14">
@@ -2995,16 +2995,16 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>0.08139534883720931</v>
+        <v>0.1022727272727273</v>
       </c>
       <c r="L31">
-        <v>0.1950113378684807</v>
+        <v>0.2838709677419355</v>
       </c>
       <c r="M31">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N31">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="9:14">
@@ -3015,16 +3015,16 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>0.1</v>
+        <v>0.07954545454545454</v>
       </c>
       <c r="L32">
-        <v>0.2546296296296297</v>
+        <v>0.3247232472324723</v>
       </c>
       <c r="M32">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="N32">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="9:14">
@@ -3035,16 +3035,16 @@
         <v>11</v>
       </c>
       <c r="K33">
-        <v>0.1319444444444444</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L33">
-        <v>0.3150984682713348</v>
+        <v>0.3435374149659864</v>
       </c>
       <c r="M33">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="N33">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="9:14">
@@ -3055,16 +3055,16 @@
         <v>12</v>
       </c>
       <c r="K34">
-        <v>0.1060606060606061</v>
+        <v>0.1</v>
       </c>
       <c r="L34">
-        <v>0.3</v>
+        <v>0.3092783505154639</v>
       </c>
       <c r="M34">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="N34">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="9:14">
@@ -3075,16 +3075,16 @@
         <v>13</v>
       </c>
       <c r="K35">
-        <v>0.1384615384615385</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="L35">
-        <v>0.3194103194103194</v>
+        <v>0.3565891472868217</v>
       </c>
       <c r="M35">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="N35">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="9:14">
@@ -3095,16 +3095,16 @@
         <v>14</v>
       </c>
       <c r="K36">
-        <v>0.1438356164383562</v>
+        <v>0.0379746835443038</v>
       </c>
       <c r="L36">
-        <v>0.3325740318906606</v>
+        <v>0.2705479452054795</v>
       </c>
       <c r="M36">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="N36">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="9:14">
@@ -3115,16 +3115,16 @@
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.1073825503355705</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="L37">
-        <v>0.3625304136253041</v>
+        <v>0.3470149253731343</v>
       </c>
       <c r="M37">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="N37">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="9:14">
@@ -3135,16 +3135,16 @@
         <v>16</v>
       </c>
       <c r="K38">
-        <v>0.09467455621301775</v>
+        <v>0.05</v>
       </c>
       <c r="L38">
-        <v>0.3995271867612293</v>
+        <v>0.364963503649635</v>
       </c>
       <c r="M38">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="N38">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="9:14">
@@ -3155,16 +3155,16 @@
         <v>17</v>
       </c>
       <c r="K39">
-        <v>0.096045197740113</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="L39">
-        <v>0.3924611973392461</v>
+        <v>0.3624595469255664</v>
       </c>
       <c r="M39">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="N39">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="9:14">
@@ -3175,16 +3175,16 @@
         <v>18</v>
       </c>
       <c r="K40">
-        <v>0.1058201058201058</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="L40">
-        <v>0.4385150812064965</v>
+        <v>0.3952702702702703</v>
       </c>
       <c r="M40">
-        <v>189</v>
+        <v>117</v>
       </c>
       <c r="N40">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="9:14">
@@ -3195,16 +3195,16 @@
         <v>19</v>
       </c>
       <c r="K41">
-        <v>0.1182795698924731</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="L41">
-        <v>0.4070021881838075</v>
+        <v>0.3495145631067961</v>
       </c>
       <c r="M41">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="N41">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="9:14">
@@ -3215,16 +3215,16 @@
         <v>20</v>
       </c>
       <c r="K42">
-        <v>0.07804878048780488</v>
+        <v>0.04464285714285714</v>
       </c>
       <c r="L42">
-        <v>0.4446854663774403</v>
+        <v>0.3660130718954248</v>
       </c>
       <c r="M42">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="N42">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3296,22 +3296,22 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>0.9545565931879846</v>
+        <v>1.852583220312426</v>
       </c>
       <c r="C4">
-        <v>8.107875986233042</v>
+        <v>6.642385548595935</v>
       </c>
       <c r="D4">
-        <v>0.8767268862911796</v>
+        <v>0.9264588329336531</v>
       </c>
       <c r="E4">
-        <v>0.3334514528703048</v>
+        <v>0.3335110637163423</v>
       </c>
       <c r="F4">
-        <v>9410000</v>
+        <v>6255000</v>
       </c>
       <c r="G4">
-        <v>8250000</v>
+        <v>5795000</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3320,16 +3320,16 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>0.8248587570621468</v>
+        <v>0.941747572815534</v>
       </c>
       <c r="L4">
-        <v>0.4492385786802031</v>
+        <v>0.3772893772893773</v>
       </c>
       <c r="M4">
-        <v>885000</v>
+        <v>515000</v>
       </c>
       <c r="N4">
-        <v>730000</v>
+        <v>485000</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3337,22 +3337,22 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>-1.0100583376388</v>
+        <v>-0.340458278724456</v>
       </c>
       <c r="C5">
-        <v>0.9491980724600928</v>
+        <v>1.852108499754602</v>
       </c>
       <c r="D5">
-        <v>0.4853801169590643</v>
+        <v>0.7048</v>
       </c>
       <c r="E5">
-        <v>0.3332742735648476</v>
+        <v>0.3332444681418288</v>
       </c>
       <c r="F5">
-        <v>9405000</v>
+        <v>6250000</v>
       </c>
       <c r="G5">
-        <v>4565000</v>
+        <v>4405000</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3361,16 +3361,16 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>0.9101796407185628</v>
+        <v>0.9557522123893806</v>
       </c>
       <c r="L5">
-        <v>0.3786848072562358</v>
+        <v>0.3645161290322581</v>
       </c>
       <c r="M5">
-        <v>835000</v>
+        <v>565000</v>
       </c>
       <c r="N5">
-        <v>760000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3378,22 +3378,22 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>-10.75813788412185</v>
+        <v>-12.96610599108593</v>
       </c>
       <c r="C6">
-        <v>-1.010537872244683</v>
+        <v>-0.3430929032834529</v>
       </c>
       <c r="D6">
-        <v>0.1047315257841574</v>
+        <v>0.0832</v>
       </c>
       <c r="E6">
-        <v>0.3332742735648476</v>
+        <v>0.3332444681418288</v>
       </c>
       <c r="F6">
-        <v>9405000</v>
+        <v>6250000</v>
       </c>
       <c r="G6">
-        <v>985000</v>
+        <v>520000</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3402,16 +3402,16 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>0.9060402684563759</v>
+        <v>0.9603960396039604</v>
       </c>
       <c r="L6">
-        <v>0.3449074074074074</v>
+        <v>0.3726937269372694</v>
       </c>
       <c r="M6">
-        <v>745000</v>
+        <v>505000</v>
       </c>
       <c r="N6">
-        <v>675000</v>
+        <v>485000</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3422,16 +3422,16 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>0.9358974358974359</v>
+        <v>0.9734513274336283</v>
       </c>
       <c r="L7">
-        <v>0.3413566739606127</v>
+        <v>0.3843537414965986</v>
       </c>
       <c r="M7">
-        <v>780000</v>
+        <v>565000</v>
       </c>
       <c r="N7">
-        <v>730000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3442,16 +3442,16 @@
         <v>12</v>
       </c>
       <c r="K8">
-        <v>0.9192546583850931</v>
+        <v>0.9607843137254902</v>
       </c>
       <c r="L8">
-        <v>0.3659090909090909</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M8">
-        <v>805000</v>
+        <v>510000</v>
       </c>
       <c r="N8">
-        <v>740000</v>
+        <v>490000</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -3462,16 +3462,16 @@
         <v>13</v>
       </c>
       <c r="K9">
-        <v>0.8931297709923665</v>
+        <v>0.9325842696629213</v>
       </c>
       <c r="L9">
-        <v>0.3218673218673219</v>
+        <v>0.3449612403100775</v>
       </c>
       <c r="M9">
-        <v>655000</v>
+        <v>445000</v>
       </c>
       <c r="N9">
-        <v>585000</v>
+        <v>415000</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -3482,16 +3482,16 @@
         <v>14</v>
       </c>
       <c r="K10">
-        <v>0.8802816901408451</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="L10">
-        <v>0.3234624145785877</v>
+        <v>0.3219178082191781</v>
       </c>
       <c r="M10">
-        <v>710000</v>
+        <v>470000</v>
       </c>
       <c r="N10">
-        <v>625000</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -3502,16 +3502,16 @@
         <v>15</v>
       </c>
       <c r="K11">
-        <v>0.8666666666666667</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="L11">
-        <v>0.3284671532846715</v>
+        <v>0.3619402985074627</v>
       </c>
       <c r="M11">
-        <v>675000</v>
+        <v>485000</v>
       </c>
       <c r="N11">
-        <v>585000</v>
+        <v>425000</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3522,16 +3522,16 @@
         <v>16</v>
       </c>
       <c r="K12">
-        <v>0.8625954198473282</v>
+        <v>0.898876404494382</v>
       </c>
       <c r="L12">
-        <v>0.3096926713947991</v>
+        <v>0.3248175182481752</v>
       </c>
       <c r="M12">
-        <v>655000</v>
+        <v>445000</v>
       </c>
       <c r="N12">
-        <v>565000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3542,16 +3542,16 @@
         <v>17</v>
       </c>
       <c r="K13">
-        <v>0.8782051282051282</v>
+        <v>0.9175257731958762</v>
       </c>
       <c r="L13">
-        <v>0.3458980044345898</v>
+        <v>0.313915857605178</v>
       </c>
       <c r="M13">
-        <v>780000</v>
+        <v>485000</v>
       </c>
       <c r="N13">
-        <v>685000</v>
+        <v>445000</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -3562,16 +3562,16 @@
         <v>18</v>
       </c>
       <c r="K14">
-        <v>0.7906976744186046</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L14">
-        <v>0.2993039443155452</v>
+        <v>0.3040540540540541</v>
       </c>
       <c r="M14">
-        <v>645000</v>
+        <v>450000</v>
       </c>
       <c r="N14">
-        <v>510000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -3582,16 +3582,16 @@
         <v>19</v>
       </c>
       <c r="K15">
-        <v>0.8270676691729323</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="L15">
-        <v>0.2910284463894967</v>
+        <v>0.2815533980582524</v>
       </c>
       <c r="M15">
-        <v>665000</v>
+        <v>435000</v>
       </c>
       <c r="N15">
-        <v>550000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3602,16 +3602,16 @@
         <v>20</v>
       </c>
       <c r="K16">
-        <v>0.8869565217391304</v>
+        <v>0.9605263157894737</v>
       </c>
       <c r="L16">
-        <v>0.2494577006507592</v>
+        <v>0.2483660130718954</v>
       </c>
       <c r="M16">
-        <v>575000</v>
+        <v>380000</v>
       </c>
       <c r="N16">
-        <v>510000</v>
+        <v>365000</v>
       </c>
     </row>
     <row r="17" spans="9:14">
@@ -3622,16 +3622,16 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>0.3333333333333333</v>
+        <v>0.54</v>
       </c>
       <c r="L17">
-        <v>0.4035532994923858</v>
+        <v>0.3663003663003663</v>
       </c>
       <c r="M17">
-        <v>795000</v>
+        <v>500000</v>
       </c>
       <c r="N17">
-        <v>265000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="18" spans="9:14">
@@ -3642,16 +3642,16 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>0.4787234042553192</v>
+        <v>0.7339449541284404</v>
       </c>
       <c r="L18">
-        <v>0.4263038548752834</v>
+        <v>0.3516129032258065</v>
       </c>
       <c r="M18">
-        <v>940000</v>
+        <v>545000</v>
       </c>
       <c r="N18">
-        <v>450000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="19" spans="9:14">
@@ -3662,16 +3662,16 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>0.4855491329479769</v>
+        <v>0.7195121951219512</v>
       </c>
       <c r="L19">
-        <v>0.400462962962963</v>
+        <v>0.3025830258302583</v>
       </c>
       <c r="M19">
-        <v>865000</v>
+        <v>410000</v>
       </c>
       <c r="N19">
-        <v>420000</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="20" spans="9:14">
@@ -3682,16 +3682,16 @@
         <v>11</v>
       </c>
       <c r="K20">
-        <v>0.4840764331210191</v>
+        <v>0.7875</v>
       </c>
       <c r="L20">
-        <v>0.3435448577680525</v>
+        <v>0.272108843537415</v>
       </c>
       <c r="M20">
-        <v>785000</v>
+        <v>400000</v>
       </c>
       <c r="N20">
-        <v>380000</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="21" spans="9:14">
@@ -3702,16 +3702,16 @@
         <v>12</v>
       </c>
       <c r="K21">
-        <v>0.5034013605442177</v>
+        <v>0.7171717171717171</v>
       </c>
       <c r="L21">
-        <v>0.3340909090909091</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="M21">
-        <v>735000</v>
+        <v>495000</v>
       </c>
       <c r="N21">
-        <v>370000</v>
+        <v>355000</v>
       </c>
     </row>
     <row r="22" spans="9:14">
@@ -3722,16 +3722,16 @@
         <v>13</v>
       </c>
       <c r="K22">
-        <v>0.4794520547945205</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L22">
-        <v>0.3587223587223587</v>
+        <v>0.2984496124031008</v>
       </c>
       <c r="M22">
-        <v>730000</v>
+        <v>385000</v>
       </c>
       <c r="N22">
-        <v>350000</v>
+        <v>280000</v>
       </c>
     </row>
     <row r="23" spans="9:14">
@@ -3742,16 +3742,16 @@
         <v>14</v>
       </c>
       <c r="K23">
-        <v>0.5033112582781457</v>
+        <v>0.7394957983193278</v>
       </c>
       <c r="L23">
-        <v>0.3439635535307517</v>
+        <v>0.4075342465753425</v>
       </c>
       <c r="M23">
-        <v>755000</v>
+        <v>595000</v>
       </c>
       <c r="N23">
-        <v>380000</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="24" spans="9:14">
@@ -3762,16 +3762,16 @@
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.4803149606299212</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L24">
-        <v>0.3090024330900243</v>
+        <v>0.291044776119403</v>
       </c>
       <c r="M24">
-        <v>635000</v>
+        <v>390000</v>
       </c>
       <c r="N24">
-        <v>305000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="25" spans="9:14">
@@ -3782,16 +3782,16 @@
         <v>16</v>
       </c>
       <c r="K25">
-        <v>0.4634146341463415</v>
+        <v>0.7529411764705882</v>
       </c>
       <c r="L25">
-        <v>0.2907801418439716</v>
+        <v>0.3102189781021898</v>
       </c>
       <c r="M25">
-        <v>615000</v>
+        <v>425000</v>
       </c>
       <c r="N25">
-        <v>285000</v>
+        <v>320000</v>
       </c>
     </row>
     <row r="26" spans="9:14">
@@ -3802,16 +3802,16 @@
         <v>17</v>
       </c>
       <c r="K26">
-        <v>0.5508474576271186</v>
+        <v>0.72</v>
       </c>
       <c r="L26">
-        <v>0.2616407982261641</v>
+        <v>0.3236245954692556</v>
       </c>
       <c r="M26">
-        <v>590000</v>
+        <v>500000</v>
       </c>
       <c r="N26">
-        <v>325000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="27" spans="9:14">
@@ -3822,13 +3822,13 @@
         <v>18</v>
       </c>
       <c r="K27">
-        <v>0.504424778761062</v>
+        <v>0.6404494382022472</v>
       </c>
       <c r="L27">
-        <v>0.2621809744779582</v>
+        <v>0.3006756756756757</v>
       </c>
       <c r="M27">
-        <v>565000</v>
+        <v>445000</v>
       </c>
       <c r="N27">
         <v>285000</v>
@@ -3842,16 +3842,16 @@
         <v>19</v>
       </c>
       <c r="K28">
-        <v>0.5507246376811594</v>
+        <v>0.7192982456140351</v>
       </c>
       <c r="L28">
-        <v>0.3019693654266958</v>
+        <v>0.3689320388349515</v>
       </c>
       <c r="M28">
-        <v>690000</v>
+        <v>570000</v>
       </c>
       <c r="N28">
-        <v>380000</v>
+        <v>410000</v>
       </c>
     </row>
     <row r="29" spans="9:14">
@@ -3862,16 +3862,16 @@
         <v>20</v>
       </c>
       <c r="K29">
-        <v>0.524822695035461</v>
+        <v>0.635593220338983</v>
       </c>
       <c r="L29">
-        <v>0.3058568329718004</v>
+        <v>0.3856209150326798</v>
       </c>
       <c r="M29">
-        <v>705000</v>
+        <v>590000</v>
       </c>
       <c r="N29">
-        <v>370000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="30" spans="9:14">
@@ -3882,16 +3882,16 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="L30">
-        <v>0.1472081218274112</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="M30">
-        <v>290000</v>
+        <v>350000</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="31" spans="9:14">
@@ -3902,16 +3902,16 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>0.08139534883720931</v>
+        <v>0.1022727272727273</v>
       </c>
       <c r="L31">
-        <v>0.1950113378684807</v>
+        <v>0.2838709677419355</v>
       </c>
       <c r="M31">
-        <v>430000</v>
+        <v>440000</v>
       </c>
       <c r="N31">
-        <v>35000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="32" spans="9:14">
@@ -3922,16 +3922,16 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>0.1</v>
+        <v>0.07954545454545454</v>
       </c>
       <c r="L32">
-        <v>0.2546296296296297</v>
+        <v>0.3247232472324723</v>
       </c>
       <c r="M32">
-        <v>550000</v>
+        <v>440000</v>
       </c>
       <c r="N32">
-        <v>55000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="33" spans="9:14">
@@ -3942,16 +3942,16 @@
         <v>11</v>
       </c>
       <c r="K33">
-        <v>0.1319444444444444</v>
+        <v>0.07920792079207921</v>
       </c>
       <c r="L33">
-        <v>0.3150984682713348</v>
+        <v>0.3435374149659864</v>
       </c>
       <c r="M33">
-        <v>720000</v>
+        <v>505000</v>
       </c>
       <c r="N33">
-        <v>95000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="34" spans="9:14">
@@ -3962,16 +3962,16 @@
         <v>12</v>
       </c>
       <c r="K34">
-        <v>0.1060606060606061</v>
+        <v>0.1</v>
       </c>
       <c r="L34">
-        <v>0.3</v>
+        <v>0.3092783505154639</v>
       </c>
       <c r="M34">
-        <v>660000</v>
+        <v>450000</v>
       </c>
       <c r="N34">
-        <v>70000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="35" spans="9:14">
@@ -3982,16 +3982,16 @@
         <v>13</v>
       </c>
       <c r="K35">
-        <v>0.1384615384615385</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="L35">
-        <v>0.3194103194103194</v>
+        <v>0.3565891472868217</v>
       </c>
       <c r="M35">
-        <v>650000</v>
+        <v>460000</v>
       </c>
       <c r="N35">
-        <v>90000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="36" spans="9:14">
@@ -4002,16 +4002,16 @@
         <v>14</v>
       </c>
       <c r="K36">
-        <v>0.1438356164383562</v>
+        <v>0.0379746835443038</v>
       </c>
       <c r="L36">
-        <v>0.3325740318906606</v>
+        <v>0.2705479452054795</v>
       </c>
       <c r="M36">
-        <v>730000</v>
+        <v>395000</v>
       </c>
       <c r="N36">
-        <v>105000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="37" spans="9:14">
@@ -4022,16 +4022,16 @@
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.1073825503355705</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="L37">
-        <v>0.3625304136253041</v>
+        <v>0.3470149253731343</v>
       </c>
       <c r="M37">
-        <v>745000</v>
+        <v>465000</v>
       </c>
       <c r="N37">
-        <v>80000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="38" spans="9:14">
@@ -4042,16 +4042,16 @@
         <v>16</v>
       </c>
       <c r="K38">
-        <v>0.09467455621301775</v>
+        <v>0.05</v>
       </c>
       <c r="L38">
-        <v>0.3995271867612293</v>
+        <v>0.364963503649635</v>
       </c>
       <c r="M38">
-        <v>845000</v>
+        <v>500000</v>
       </c>
       <c r="N38">
-        <v>80000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="39" spans="9:14">
@@ -4062,16 +4062,16 @@
         <v>17</v>
       </c>
       <c r="K39">
-        <v>0.096045197740113</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="L39">
-        <v>0.3924611973392461</v>
+        <v>0.3624595469255664</v>
       </c>
       <c r="M39">
-        <v>885000</v>
+        <v>560000</v>
       </c>
       <c r="N39">
-        <v>85000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="40" spans="9:14">
@@ -4082,16 +4082,16 @@
         <v>18</v>
       </c>
       <c r="K40">
-        <v>0.1058201058201058</v>
+        <v>0.1025641025641026</v>
       </c>
       <c r="L40">
-        <v>0.4385150812064965</v>
+        <v>0.3952702702702703</v>
       </c>
       <c r="M40">
-        <v>945000</v>
+        <v>585000</v>
       </c>
       <c r="N40">
-        <v>100000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="41" spans="9:14">
@@ -4102,16 +4102,16 @@
         <v>19</v>
       </c>
       <c r="K41">
-        <v>0.1182795698924731</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="L41">
-        <v>0.4070021881838075</v>
+        <v>0.3495145631067961</v>
       </c>
       <c r="M41">
-        <v>930000</v>
+        <v>540000</v>
       </c>
       <c r="N41">
-        <v>110000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="42" spans="9:14">
@@ -4122,16 +4122,16 @@
         <v>20</v>
       </c>
       <c r="K42">
-        <v>0.07804878048780488</v>
+        <v>0.04464285714285714</v>
       </c>
       <c r="L42">
-        <v>0.4446854663774403</v>
+        <v>0.3660130718954248</v>
       </c>
       <c r="M42">
-        <v>1025000</v>
+        <v>560000</v>
       </c>
       <c r="N42">
-        <v>80000</v>
+        <v>25000</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/pd_css_cross/Segments3_report.xlsx
+++ b/outputs/pd_css_cross/Segments3_report.xlsx
@@ -249,43 +249,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.941747572815534</c:v>
+                  <c:v>0.8248587570621468</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9557522123893806</c:v>
+                  <c:v>0.9101796407185628</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9603960396039604</c:v>
+                  <c:v>0.9060402684563759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9734513274336283</c:v>
+                  <c:v>0.9358974358974359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9607843137254902</c:v>
+                  <c:v>0.9192546583850931</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9325842696629213</c:v>
+                  <c:v>0.8931297709923665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.9148936170212766</c:v>
+                  <c:v>0.8802816901408451</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8762886597938144</c:v>
+                  <c:v>0.8666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.898876404494382</c:v>
+                  <c:v>0.8625954198473282</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9175257731958762</c:v>
+                  <c:v>0.8782051282051282</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8666666666666667</c:v>
+                  <c:v>0.7906976744186046</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8620689655172413</c:v>
+                  <c:v>0.8270676691729323</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.9605263157894737</c:v>
+                  <c:v>0.8869565217391304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -363,43 +363,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.54</c:v>
+                  <c:v>0.3333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7339449541284404</c:v>
+                  <c:v>0.4787234042553192</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7195121951219512</c:v>
+                  <c:v>0.4855491329479769</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.7875</c:v>
+                  <c:v>0.4840764331210191</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7171717171717171</c:v>
+                  <c:v>0.5034013605442177</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7272727272727273</c:v>
+                  <c:v>0.4794520547945205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.7394957983193278</c:v>
+                  <c:v>0.5033112582781457</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.7692307692307693</c:v>
+                  <c:v>0.4803149606299212</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.7529411764705882</c:v>
+                  <c:v>0.4634146341463415</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.72</c:v>
+                  <c:v>0.5508474576271186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.6404494382022472</c:v>
+                  <c:v>0.504424778761062</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.7192982456140351</c:v>
+                  <c:v>0.5507246376811594</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.635593220338983</c:v>
+                  <c:v>0.524822695035461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -477,43 +477,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.04285714285714286</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1022727272727273</c:v>
+                  <c:v>0.08139534883720931</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.07954545454545454</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.07920792079207921</c:v>
+                  <c:v>0.1319444444444444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1</c:v>
+                  <c:v>0.1060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1739130434782609</c:v>
+                  <c:v>0.1384615384615385</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0379746835443038</c:v>
+                  <c:v>0.1438356164383562</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.07526881720430108</c:v>
+                  <c:v>0.1073825503355705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.05</c:v>
+                  <c:v>0.09467455621301775</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1071428571428571</c:v>
+                  <c:v>0.096045197740113</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1025641025641026</c:v>
+                  <c:v>0.1058201058201058</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.07407407407407407</c:v>
+                  <c:v>0.1182795698924731</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.04464285714285714</c:v>
+                  <c:v>0.07804878048780488</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -691,43 +691,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3772893772893773</c:v>
+                  <c:v>0.4492385786802031</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3645161290322581</c:v>
+                  <c:v>0.3786848072562358</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3726937269372694</c:v>
+                  <c:v>0.3449074074074074</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3843537414965986</c:v>
+                  <c:v>0.3413566739606127</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3505154639175257</c:v>
+                  <c:v>0.3659090909090909</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3449612403100775</c:v>
+                  <c:v>0.3218673218673219</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3219178082191781</c:v>
+                  <c:v>0.3234624145785877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3619402985074627</c:v>
+                  <c:v>0.3284671532846715</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3248175182481752</c:v>
+                  <c:v>0.3096926713947991</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.313915857605178</c:v>
+                  <c:v>0.3458980044345898</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3040540540540541</c:v>
+                  <c:v>0.2993039443155452</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2815533980582524</c:v>
+                  <c:v>0.2910284463894967</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2483660130718954</c:v>
+                  <c:v>0.2494577006507592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -805,43 +805,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3663003663003663</c:v>
+                  <c:v>0.4035532994923858</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3516129032258065</c:v>
+                  <c:v>0.4263038548752834</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3025830258302583</c:v>
+                  <c:v>0.400462962962963</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.272108843537415</c:v>
+                  <c:v>0.3435448577680525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3402061855670103</c:v>
+                  <c:v>0.3340909090909091</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2984496124031008</c:v>
+                  <c:v>0.3587223587223587</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4075342465753425</c:v>
+                  <c:v>0.3439635535307517</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.291044776119403</c:v>
+                  <c:v>0.3090024330900243</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3102189781021898</c:v>
+                  <c:v>0.2907801418439716</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3236245954692556</c:v>
+                  <c:v>0.2616407982261641</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3006756756756757</c:v>
+                  <c:v>0.2621809744779582</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3689320388349515</c:v>
+                  <c:v>0.3019693654266958</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3856209150326798</c:v>
+                  <c:v>0.3058568329718004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -919,43 +919,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.2564102564102564</c:v>
+                  <c:v>0.1472081218274112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2838709677419355</c:v>
+                  <c:v>0.1950113378684807</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3247232472324723</c:v>
+                  <c:v>0.2546296296296297</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3435374149659864</c:v>
+                  <c:v>0.3150984682713348</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3092783505154639</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3565891472868217</c:v>
+                  <c:v>0.3194103194103194</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2705479452054795</c:v>
+                  <c:v>0.3325740318906606</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3470149253731343</c:v>
+                  <c:v>0.3625304136253041</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.364963503649635</c:v>
+                  <c:v>0.3995271867612293</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3624595469255664</c:v>
+                  <c:v>0.3924611973392461</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3952702702702703</c:v>
+                  <c:v>0.4385150812064965</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3495145631067961</c:v>
+                  <c:v>0.4070021881838075</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3660130718954248</c:v>
+                  <c:v>0.4446854663774403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1133,43 +1133,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.941747572815534</c:v>
+                  <c:v>0.8248587570621468</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9557522123893806</c:v>
+                  <c:v>0.9101796407185628</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9603960396039604</c:v>
+                  <c:v>0.9060402684563759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9734513274336283</c:v>
+                  <c:v>0.9358974358974359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9607843137254902</c:v>
+                  <c:v>0.9192546583850931</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9325842696629213</c:v>
+                  <c:v>0.8931297709923665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.9148936170212766</c:v>
+                  <c:v>0.8802816901408451</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8762886597938144</c:v>
+                  <c:v>0.8666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.898876404494382</c:v>
+                  <c:v>0.8625954198473282</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9175257731958762</c:v>
+                  <c:v>0.8782051282051282</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8666666666666667</c:v>
+                  <c:v>0.7906976744186046</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8620689655172413</c:v>
+                  <c:v>0.8270676691729323</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.9605263157894737</c:v>
+                  <c:v>0.8869565217391304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1247,43 +1247,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.54</c:v>
+                  <c:v>0.3333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7339449541284404</c:v>
+                  <c:v>0.4787234042553192</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7195121951219512</c:v>
+                  <c:v>0.4855491329479769</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.7875</c:v>
+                  <c:v>0.4840764331210191</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7171717171717171</c:v>
+                  <c:v>0.5034013605442177</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7272727272727273</c:v>
+                  <c:v>0.4794520547945205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.7394957983193278</c:v>
+                  <c:v>0.5033112582781457</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.7692307692307693</c:v>
+                  <c:v>0.4803149606299212</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.7529411764705882</c:v>
+                  <c:v>0.4634146341463415</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.72</c:v>
+                  <c:v>0.5508474576271186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.6404494382022472</c:v>
+                  <c:v>0.504424778761062</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.7192982456140351</c:v>
+                  <c:v>0.5507246376811594</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.635593220338983</c:v>
+                  <c:v>0.524822695035461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1361,43 +1361,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.04285714285714286</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1022727272727273</c:v>
+                  <c:v>0.08139534883720931</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.07954545454545454</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.07920792079207921</c:v>
+                  <c:v>0.1319444444444444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1</c:v>
+                  <c:v>0.1060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1739130434782609</c:v>
+                  <c:v>0.1384615384615385</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0379746835443038</c:v>
+                  <c:v>0.1438356164383562</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.07526881720430108</c:v>
+                  <c:v>0.1073825503355705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.05</c:v>
+                  <c:v>0.09467455621301775</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1071428571428571</c:v>
+                  <c:v>0.096045197740113</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1025641025641026</c:v>
+                  <c:v>0.1058201058201058</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.07407407407407407</c:v>
+                  <c:v>0.1182795698924731</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.04464285714285714</c:v>
+                  <c:v>0.07804878048780488</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1575,43 +1575,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3772893772893773</c:v>
+                  <c:v>0.4492385786802031</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3645161290322581</c:v>
+                  <c:v>0.3786848072562358</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3726937269372694</c:v>
+                  <c:v>0.3449074074074074</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3843537414965986</c:v>
+                  <c:v>0.3413566739606127</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3505154639175257</c:v>
+                  <c:v>0.3659090909090909</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3449612403100775</c:v>
+                  <c:v>0.3218673218673219</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3219178082191781</c:v>
+                  <c:v>0.3234624145785877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3619402985074627</c:v>
+                  <c:v>0.3284671532846715</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3248175182481752</c:v>
+                  <c:v>0.3096926713947991</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.313915857605178</c:v>
+                  <c:v>0.3458980044345898</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3040540540540541</c:v>
+                  <c:v>0.2993039443155452</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2815533980582524</c:v>
+                  <c:v>0.2910284463894967</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2483660130718954</c:v>
+                  <c:v>0.2494577006507592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1689,43 +1689,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.3663003663003663</c:v>
+                  <c:v>0.4035532994923858</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3516129032258065</c:v>
+                  <c:v>0.4263038548752834</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3025830258302583</c:v>
+                  <c:v>0.400462962962963</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.272108843537415</c:v>
+                  <c:v>0.3435448577680525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3402061855670103</c:v>
+                  <c:v>0.3340909090909091</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2984496124031008</c:v>
+                  <c:v>0.3587223587223587</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4075342465753425</c:v>
+                  <c:v>0.3439635535307517</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.291044776119403</c:v>
+                  <c:v>0.3090024330900243</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3102189781021898</c:v>
+                  <c:v>0.2907801418439716</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3236245954692556</c:v>
+                  <c:v>0.2616407982261641</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3006756756756757</c:v>
+                  <c:v>0.2621809744779582</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3689320388349515</c:v>
+                  <c:v>0.3019693654266958</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3856209150326798</c:v>
+                  <c:v>0.3058568329718004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1803,43 +1803,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0.2564102564102564</c:v>
+                  <c:v>0.1472081218274112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2838709677419355</c:v>
+                  <c:v>0.1950113378684807</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3247232472324723</c:v>
+                  <c:v>0.2546296296296297</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3435374149659864</c:v>
+                  <c:v>0.3150984682713348</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3092783505154639</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3565891472868217</c:v>
+                  <c:v>0.3194103194103194</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2705479452054795</c:v>
+                  <c:v>0.3325740318906606</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3470149253731343</c:v>
+                  <c:v>0.3625304136253041</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.364963503649635</c:v>
+                  <c:v>0.3995271867612293</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3624595469255664</c:v>
+                  <c:v>0.3924611973392461</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3952702702702703</c:v>
+                  <c:v>0.4385150812064965</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3495145631067961</c:v>
+                  <c:v>0.4070021881838075</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3660130718954248</c:v>
+                  <c:v>0.4446854663774403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2389,22 +2389,22 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>1.852583220312426</v>
+        <v>0.9545565931879846</v>
       </c>
       <c r="C4">
-        <v>6.642385548595935</v>
+        <v>8.107875986233042</v>
       </c>
       <c r="D4">
-        <v>0.9264588329336531</v>
+        <v>0.8767268862911796</v>
       </c>
       <c r="E4">
-        <v>0.3335110637163423</v>
+        <v>0.3334514528703048</v>
       </c>
       <c r="F4">
-        <v>1251</v>
+        <v>1882</v>
       </c>
       <c r="G4">
-        <v>1159</v>
+        <v>1650</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2413,16 +2413,16 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>0.941747572815534</v>
+        <v>0.8248587570621468</v>
       </c>
       <c r="L4">
-        <v>0.3772893772893773</v>
+        <v>0.4492385786802031</v>
       </c>
       <c r="M4">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="N4">
-        <v>97</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2430,22 +2430,22 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>-0.340458278724456</v>
+        <v>-1.0100583376388</v>
       </c>
       <c r="C5">
-        <v>1.852108499754602</v>
+        <v>0.9491980724600928</v>
       </c>
       <c r="D5">
-        <v>0.7048</v>
+        <v>0.4853801169590643</v>
       </c>
       <c r="E5">
-        <v>0.3332444681418288</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F5">
-        <v>1250</v>
+        <v>1881</v>
       </c>
       <c r="G5">
-        <v>881</v>
+        <v>913</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2454,16 +2454,16 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>0.9557522123893806</v>
+        <v>0.9101796407185628</v>
       </c>
       <c r="L5">
-        <v>0.3645161290322581</v>
+        <v>0.3786848072562358</v>
       </c>
       <c r="M5">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="N5">
-        <v>108</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2471,22 +2471,22 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>-12.96610599108593</v>
+        <v>-10.75813788412185</v>
       </c>
       <c r="C6">
-        <v>-0.3430929032834529</v>
+        <v>-1.010537872244683</v>
       </c>
       <c r="D6">
-        <v>0.0832</v>
+        <v>0.1047315257841574</v>
       </c>
       <c r="E6">
-        <v>0.3332444681418288</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F6">
-        <v>1250</v>
+        <v>1881</v>
       </c>
       <c r="G6">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2495,16 +2495,16 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>0.9603960396039604</v>
+        <v>0.9060402684563759</v>
       </c>
       <c r="L6">
-        <v>0.3726937269372694</v>
+        <v>0.3449074074074074</v>
       </c>
       <c r="M6">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="N6">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2515,16 +2515,16 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>0.9734513274336283</v>
+        <v>0.9358974358974359</v>
       </c>
       <c r="L7">
-        <v>0.3843537414965986</v>
+        <v>0.3413566739606127</v>
       </c>
       <c r="M7">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="N7">
-        <v>110</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -2535,16 +2535,16 @@
         <v>12</v>
       </c>
       <c r="K8">
-        <v>0.9607843137254902</v>
+        <v>0.9192546583850931</v>
       </c>
       <c r="L8">
-        <v>0.3505154639175257</v>
+        <v>0.3659090909090909</v>
       </c>
       <c r="M8">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="N8">
-        <v>98</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2555,16 +2555,16 @@
         <v>13</v>
       </c>
       <c r="K9">
-        <v>0.9325842696629213</v>
+        <v>0.8931297709923665</v>
       </c>
       <c r="L9">
-        <v>0.3449612403100775</v>
+        <v>0.3218673218673219</v>
       </c>
       <c r="M9">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="N9">
-        <v>83</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2575,16 +2575,16 @@
         <v>14</v>
       </c>
       <c r="K10">
-        <v>0.9148936170212766</v>
+        <v>0.8802816901408451</v>
       </c>
       <c r="L10">
-        <v>0.3219178082191781</v>
+        <v>0.3234624145785877</v>
       </c>
       <c r="M10">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="N10">
-        <v>86</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2595,16 +2595,16 @@
         <v>15</v>
       </c>
       <c r="K11">
-        <v>0.8762886597938144</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L11">
-        <v>0.3619402985074627</v>
+        <v>0.3284671532846715</v>
       </c>
       <c r="M11">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="N11">
-        <v>85</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2615,16 +2615,16 @@
         <v>16</v>
       </c>
       <c r="K12">
-        <v>0.898876404494382</v>
+        <v>0.8625954198473282</v>
       </c>
       <c r="L12">
-        <v>0.3248175182481752</v>
+        <v>0.3096926713947991</v>
       </c>
       <c r="M12">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="N12">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2635,16 +2635,16 @@
         <v>17</v>
       </c>
       <c r="K13">
-        <v>0.9175257731958762</v>
+        <v>0.8782051282051282</v>
       </c>
       <c r="L13">
-        <v>0.313915857605178</v>
+        <v>0.3458980044345898</v>
       </c>
       <c r="M13">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="N13">
-        <v>89</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -2655,16 +2655,16 @@
         <v>18</v>
       </c>
       <c r="K14">
-        <v>0.8666666666666667</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="L14">
-        <v>0.3040540540540541</v>
+        <v>0.2993039443155452</v>
       </c>
       <c r="M14">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="N14">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2675,16 +2675,16 @@
         <v>19</v>
       </c>
       <c r="K15">
-        <v>0.8620689655172413</v>
+        <v>0.8270676691729323</v>
       </c>
       <c r="L15">
-        <v>0.2815533980582524</v>
+        <v>0.2910284463894967</v>
       </c>
       <c r="M15">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="N15">
-        <v>75</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2695,16 +2695,16 @@
         <v>20</v>
       </c>
       <c r="K16">
-        <v>0.9605263157894737</v>
+        <v>0.8869565217391304</v>
       </c>
       <c r="L16">
-        <v>0.2483660130718954</v>
+        <v>0.2494577006507592</v>
       </c>
       <c r="M16">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="N16">
-        <v>73</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="9:14">
@@ -2715,16 +2715,16 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>0.54</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L17">
-        <v>0.3663003663003663</v>
+        <v>0.4035532994923858</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="N17">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="9:14">
@@ -2735,16 +2735,16 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>0.7339449541284404</v>
+        <v>0.4787234042553192</v>
       </c>
       <c r="L18">
-        <v>0.3516129032258065</v>
+        <v>0.4263038548752834</v>
       </c>
       <c r="M18">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="N18">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="9:14">
@@ -2755,16 +2755,16 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>0.7195121951219512</v>
+        <v>0.4855491329479769</v>
       </c>
       <c r="L19">
-        <v>0.3025830258302583</v>
+        <v>0.400462962962963</v>
       </c>
       <c r="M19">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="N19">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="9:14">
@@ -2775,16 +2775,16 @@
         <v>11</v>
       </c>
       <c r="K20">
-        <v>0.7875</v>
+        <v>0.4840764331210191</v>
       </c>
       <c r="L20">
-        <v>0.272108843537415</v>
+        <v>0.3435448577680525</v>
       </c>
       <c r="M20">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="N20">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="9:14">
@@ -2795,16 +2795,16 @@
         <v>12</v>
       </c>
       <c r="K21">
-        <v>0.7171717171717171</v>
+        <v>0.5034013605442177</v>
       </c>
       <c r="L21">
-        <v>0.3402061855670103</v>
+        <v>0.3340909090909091</v>
       </c>
       <c r="M21">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="N21">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="9:14">
@@ -2815,16 +2815,16 @@
         <v>13</v>
       </c>
       <c r="K22">
-        <v>0.7272727272727273</v>
+        <v>0.4794520547945205</v>
       </c>
       <c r="L22">
-        <v>0.2984496124031008</v>
+        <v>0.3587223587223587</v>
       </c>
       <c r="M22">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="N22">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="9:14">
@@ -2835,16 +2835,16 @@
         <v>14</v>
       </c>
       <c r="K23">
-        <v>0.7394957983193278</v>
+        <v>0.5033112582781457</v>
       </c>
       <c r="L23">
-        <v>0.4075342465753425</v>
+        <v>0.3439635535307517</v>
       </c>
       <c r="M23">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="N23">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="9:14">
@@ -2855,16 +2855,16 @@
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.7692307692307693</v>
+        <v>0.4803149606299212</v>
       </c>
       <c r="L24">
-        <v>0.291044776119403</v>
+        <v>0.3090024330900243</v>
       </c>
       <c r="M24">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="N24">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="9:14">
@@ -2875,16 +2875,16 @@
         <v>16</v>
       </c>
       <c r="K25">
-        <v>0.7529411764705882</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="L25">
-        <v>0.3102189781021898</v>
+        <v>0.2907801418439716</v>
       </c>
       <c r="M25">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="N25">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="9:14">
@@ -2895,16 +2895,16 @@
         <v>17</v>
       </c>
       <c r="K26">
-        <v>0.72</v>
+        <v>0.5508474576271186</v>
       </c>
       <c r="L26">
-        <v>0.3236245954692556</v>
+        <v>0.2616407982261641</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="N26">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="9:14">
@@ -2915,13 +2915,13 @@
         <v>18</v>
       </c>
       <c r="K27">
-        <v>0.6404494382022472</v>
+        <v>0.504424778761062</v>
       </c>
       <c r="L27">
-        <v>0.3006756756756757</v>
+        <v>0.2621809744779582</v>
       </c>
       <c r="M27">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="N27">
         <v>57</v>
@@ -2935,16 +2935,16 @@
         <v>19</v>
       </c>
       <c r="K28">
-        <v>0.7192982456140351</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="L28">
-        <v>0.3689320388349515</v>
+        <v>0.3019693654266958</v>
       </c>
       <c r="M28">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="N28">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="9:14">
@@ -2955,16 +2955,16 @@
         <v>20</v>
       </c>
       <c r="K29">
-        <v>0.635593220338983</v>
+        <v>0.524822695035461</v>
       </c>
       <c r="L29">
-        <v>0.3856209150326798</v>
+        <v>0.3058568329718004</v>
       </c>
       <c r="M29">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="N29">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="9:14">
@@ -2975,16 +2975,16 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>0.04285714285714286</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>0.2564102564102564</v>
+        <v>0.1472081218274112</v>
       </c>
       <c r="M30">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="9:14">
@@ -2995,16 +2995,16 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>0.1022727272727273</v>
+        <v>0.08139534883720931</v>
       </c>
       <c r="L31">
-        <v>0.2838709677419355</v>
+        <v>0.1950113378684807</v>
       </c>
       <c r="M31">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N31">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="9:14">
@@ -3015,16 +3015,16 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>0.07954545454545454</v>
+        <v>0.1</v>
       </c>
       <c r="L32">
-        <v>0.3247232472324723</v>
+        <v>0.2546296296296297</v>
       </c>
       <c r="M32">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="9:14">
@@ -3035,16 +3035,16 @@
         <v>11</v>
       </c>
       <c r="K33">
-        <v>0.07920792079207921</v>
+        <v>0.1319444444444444</v>
       </c>
       <c r="L33">
-        <v>0.3435374149659864</v>
+        <v>0.3150984682713348</v>
       </c>
       <c r="M33">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="N33">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="9:14">
@@ -3055,16 +3055,16 @@
         <v>12</v>
       </c>
       <c r="K34">
-        <v>0.1</v>
+        <v>0.1060606060606061</v>
       </c>
       <c r="L34">
-        <v>0.3092783505154639</v>
+        <v>0.3</v>
       </c>
       <c r="M34">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="N34">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="9:14">
@@ -3075,16 +3075,16 @@
         <v>13</v>
       </c>
       <c r="K35">
-        <v>0.1739130434782609</v>
+        <v>0.1384615384615385</v>
       </c>
       <c r="L35">
-        <v>0.3565891472868217</v>
+        <v>0.3194103194103194</v>
       </c>
       <c r="M35">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="N35">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="9:14">
@@ -3095,16 +3095,16 @@
         <v>14</v>
       </c>
       <c r="K36">
-        <v>0.0379746835443038</v>
+        <v>0.1438356164383562</v>
       </c>
       <c r="L36">
-        <v>0.2705479452054795</v>
+        <v>0.3325740318906606</v>
       </c>
       <c r="M36">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="9:14">
@@ -3115,16 +3115,16 @@
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.07526881720430108</v>
+        <v>0.1073825503355705</v>
       </c>
       <c r="L37">
-        <v>0.3470149253731343</v>
+        <v>0.3625304136253041</v>
       </c>
       <c r="M37">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="N37">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="9:14">
@@ -3135,16 +3135,16 @@
         <v>16</v>
       </c>
       <c r="K38">
-        <v>0.05</v>
+        <v>0.09467455621301775</v>
       </c>
       <c r="L38">
-        <v>0.364963503649635</v>
+        <v>0.3995271867612293</v>
       </c>
       <c r="M38">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="9:14">
@@ -3155,16 +3155,16 @@
         <v>17</v>
       </c>
       <c r="K39">
-        <v>0.1071428571428571</v>
+        <v>0.096045197740113</v>
       </c>
       <c r="L39">
-        <v>0.3624595469255664</v>
+        <v>0.3924611973392461</v>
       </c>
       <c r="M39">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="N39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="9:14">
@@ -3175,16 +3175,16 @@
         <v>18</v>
       </c>
       <c r="K40">
-        <v>0.1025641025641026</v>
+        <v>0.1058201058201058</v>
       </c>
       <c r="L40">
-        <v>0.3952702702702703</v>
+        <v>0.4385150812064965</v>
       </c>
       <c r="M40">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="N40">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="9:14">
@@ -3195,16 +3195,16 @@
         <v>19</v>
       </c>
       <c r="K41">
-        <v>0.07407407407407407</v>
+        <v>0.1182795698924731</v>
       </c>
       <c r="L41">
-        <v>0.3495145631067961</v>
+        <v>0.4070021881838075</v>
       </c>
       <c r="M41">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="N41">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="9:14">
@@ -3215,16 +3215,16 @@
         <v>20</v>
       </c>
       <c r="K42">
-        <v>0.04464285714285714</v>
+        <v>0.07804878048780488</v>
       </c>
       <c r="L42">
-        <v>0.3660130718954248</v>
+        <v>0.4446854663774403</v>
       </c>
       <c r="M42">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3296,22 +3296,22 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>1.852583220312426</v>
+        <v>0.9545565931879846</v>
       </c>
       <c r="C4">
-        <v>6.642385548595935</v>
+        <v>8.107875986233042</v>
       </c>
       <c r="D4">
-        <v>0.9264588329336531</v>
+        <v>0.8767268862911796</v>
       </c>
       <c r="E4">
-        <v>0.3335110637163423</v>
+        <v>0.3334514528703048</v>
       </c>
       <c r="F4">
-        <v>6255000</v>
+        <v>9410000</v>
       </c>
       <c r="G4">
-        <v>5795000</v>
+        <v>8250000</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3320,16 +3320,16 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>0.941747572815534</v>
+        <v>0.8248587570621468</v>
       </c>
       <c r="L4">
-        <v>0.3772893772893773</v>
+        <v>0.4492385786802031</v>
       </c>
       <c r="M4">
-        <v>515000</v>
+        <v>885000</v>
       </c>
       <c r="N4">
-        <v>485000</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3337,22 +3337,22 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>-0.340458278724456</v>
+        <v>-1.0100583376388</v>
       </c>
       <c r="C5">
-        <v>1.852108499754602</v>
+        <v>0.9491980724600928</v>
       </c>
       <c r="D5">
-        <v>0.7048</v>
+        <v>0.4853801169590643</v>
       </c>
       <c r="E5">
-        <v>0.3332444681418288</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F5">
-        <v>6250000</v>
+        <v>9405000</v>
       </c>
       <c r="G5">
-        <v>4405000</v>
+        <v>4565000</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3361,16 +3361,16 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>0.9557522123893806</v>
+        <v>0.9101796407185628</v>
       </c>
       <c r="L5">
-        <v>0.3645161290322581</v>
+        <v>0.3786848072562358</v>
       </c>
       <c r="M5">
-        <v>565000</v>
+        <v>835000</v>
       </c>
       <c r="N5">
-        <v>540000</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3378,22 +3378,22 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>-12.96610599108593</v>
+        <v>-10.75813788412185</v>
       </c>
       <c r="C6">
-        <v>-0.3430929032834529</v>
+        <v>-1.010537872244683</v>
       </c>
       <c r="D6">
-        <v>0.0832</v>
+        <v>0.1047315257841574</v>
       </c>
       <c r="E6">
-        <v>0.3332444681418288</v>
+        <v>0.3332742735648476</v>
       </c>
       <c r="F6">
-        <v>6250000</v>
+        <v>9405000</v>
       </c>
       <c r="G6">
-        <v>520000</v>
+        <v>985000</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3402,16 +3402,16 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>0.9603960396039604</v>
+        <v>0.9060402684563759</v>
       </c>
       <c r="L6">
-        <v>0.3726937269372694</v>
+        <v>0.3449074074074074</v>
       </c>
       <c r="M6">
-        <v>505000</v>
+        <v>745000</v>
       </c>
       <c r="N6">
-        <v>485000</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3422,16 +3422,16 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>0.9734513274336283</v>
+        <v>0.9358974358974359</v>
       </c>
       <c r="L7">
-        <v>0.3843537414965986</v>
+        <v>0.3413566739606127</v>
       </c>
       <c r="M7">
-        <v>565000</v>
+        <v>780000</v>
       </c>
       <c r="N7">
-        <v>550000</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3442,16 +3442,16 @@
         <v>12</v>
       </c>
       <c r="K8">
-        <v>0.9607843137254902</v>
+        <v>0.9192546583850931</v>
       </c>
       <c r="L8">
-        <v>0.3505154639175257</v>
+        <v>0.3659090909090909</v>
       </c>
       <c r="M8">
-        <v>510000</v>
+        <v>805000</v>
       </c>
       <c r="N8">
-        <v>490000</v>
+        <v>740000</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -3462,16 +3462,16 @@
         <v>13</v>
       </c>
       <c r="K9">
-        <v>0.9325842696629213</v>
+        <v>0.8931297709923665</v>
       </c>
       <c r="L9">
-        <v>0.3449612403100775</v>
+        <v>0.3218673218673219</v>
       </c>
       <c r="M9">
-        <v>445000</v>
+        <v>655000</v>
       </c>
       <c r="N9">
-        <v>415000</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -3482,16 +3482,16 @@
         <v>14</v>
       </c>
       <c r="K10">
-        <v>0.9148936170212766</v>
+        <v>0.8802816901408451</v>
       </c>
       <c r="L10">
-        <v>0.3219178082191781</v>
+        <v>0.3234624145785877</v>
       </c>
       <c r="M10">
-        <v>470000</v>
+        <v>710000</v>
       </c>
       <c r="N10">
-        <v>430000</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -3502,16 +3502,16 @@
         <v>15</v>
       </c>
       <c r="K11">
-        <v>0.8762886597938144</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L11">
-        <v>0.3619402985074627</v>
+        <v>0.3284671532846715</v>
       </c>
       <c r="M11">
-        <v>485000</v>
+        <v>675000</v>
       </c>
       <c r="N11">
-        <v>425000</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3522,16 +3522,16 @@
         <v>16</v>
       </c>
       <c r="K12">
-        <v>0.898876404494382</v>
+        <v>0.8625954198473282</v>
       </c>
       <c r="L12">
-        <v>0.3248175182481752</v>
+        <v>0.3096926713947991</v>
       </c>
       <c r="M12">
-        <v>445000</v>
+        <v>655000</v>
       </c>
       <c r="N12">
-        <v>400000</v>
+        <v>565000</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -3542,16 +3542,16 @@
         <v>17</v>
       </c>
       <c r="K13">
-        <v>0.9175257731958762</v>
+        <v>0.8782051282051282</v>
       </c>
       <c r="L13">
-        <v>0.313915857605178</v>
+        <v>0.3458980044345898</v>
       </c>
       <c r="M13">
-        <v>485000</v>
+        <v>780000</v>
       </c>
       <c r="N13">
-        <v>445000</v>
+        <v>685000</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -3562,16 +3562,16 @@
         <v>18</v>
       </c>
       <c r="K14">
-        <v>0.8666666666666667</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="L14">
-        <v>0.3040540540540541</v>
+        <v>0.2993039443155452</v>
       </c>
       <c r="M14">
-        <v>450000</v>
+        <v>645000</v>
       </c>
       <c r="N14">
-        <v>390000</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -3582,16 +3582,16 @@
         <v>19</v>
       </c>
       <c r="K15">
-        <v>0.8620689655172413</v>
+        <v>0.8270676691729323</v>
       </c>
       <c r="L15">
-        <v>0.2815533980582524</v>
+        <v>0.2910284463894967</v>
       </c>
       <c r="M15">
-        <v>435000</v>
+        <v>665000</v>
       </c>
       <c r="N15">
-        <v>375000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3602,16 +3602,16 @@
         <v>20</v>
       </c>
       <c r="K16">
-        <v>0.9605263157894737</v>
+        <v>0.8869565217391304</v>
       </c>
       <c r="L16">
-        <v>0.2483660130718954</v>
+        <v>0.2494577006507592</v>
       </c>
       <c r="M16">
-        <v>380000</v>
+        <v>575000</v>
       </c>
       <c r="N16">
-        <v>365000</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="17" spans="9:14">
@@ -3622,16 +3622,16 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>0.54</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L17">
-        <v>0.3663003663003663</v>
+        <v>0.4035532994923858</v>
       </c>
       <c r="M17">
-        <v>500000</v>
+        <v>795000</v>
       </c>
       <c r="N17">
-        <v>270000</v>
+        <v>265000</v>
       </c>
     </row>
     <row r="18" spans="9:14">
@@ -3642,16 +3642,16 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>0.7339449541284404</v>
+        <v>0.4787234042553192</v>
       </c>
       <c r="L18">
-        <v>0.3516129032258065</v>
+        <v>0.4263038548752834</v>
       </c>
       <c r="M18">
-        <v>545000</v>
+        <v>940000</v>
       </c>
       <c r="N18">
-        <v>400000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="19" spans="9:14">
@@ -3662,16 +3662,16 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>0.7195121951219512</v>
+        <v>0.4855491329479769</v>
       </c>
       <c r="L19">
-        <v>0.3025830258302583</v>
+        <v>0.400462962962963</v>
       </c>
       <c r="M19">
-        <v>410000</v>
+        <v>865000</v>
       </c>
       <c r="N19">
-        <v>295000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="20" spans="9:14">
@@ -3682,16 +3682,16 @@
         <v>11</v>
       </c>
       <c r="K20">
-        <v>0.7875</v>
+        <v>0.4840764331210191</v>
       </c>
       <c r="L20">
-        <v>0.272108843537415</v>
+        <v>0.3435448577680525</v>
       </c>
       <c r="M20">
-        <v>400000</v>
+        <v>785000</v>
       </c>
       <c r="N20">
-        <v>315000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="21" spans="9:14">
@@ -3702,16 +3702,16 @@
         <v>12</v>
       </c>
       <c r="K21">
-        <v>0.7171717171717171</v>
+        <v>0.5034013605442177</v>
       </c>
       <c r="L21">
-        <v>0.3402061855670103</v>
+        <v>0.3340909090909091</v>
       </c>
       <c r="M21">
-        <v>495000</v>
+        <v>735000</v>
       </c>
       <c r="N21">
-        <v>355000</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="22" spans="9:14">
@@ -3722,16 +3722,16 @@
         <v>13</v>
       </c>
       <c r="K22">
-        <v>0.7272727272727273</v>
+        <v>0.4794520547945205</v>
       </c>
       <c r="L22">
-        <v>0.2984496124031008</v>
+        <v>0.3587223587223587</v>
       </c>
       <c r="M22">
-        <v>385000</v>
+        <v>730000</v>
       </c>
       <c r="N22">
-        <v>280000</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="23" spans="9:14">
@@ -3742,16 +3742,16 @@
         <v>14</v>
       </c>
       <c r="K23">
-        <v>0.7394957983193278</v>
+        <v>0.5033112582781457</v>
       </c>
       <c r="L23">
-        <v>0.4075342465753425</v>
+        <v>0.3439635535307517</v>
       </c>
       <c r="M23">
-        <v>595000</v>
+        <v>755000</v>
       </c>
       <c r="N23">
-        <v>440000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="24" spans="9:14">
@@ -3762,16 +3762,16 @@
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.7692307692307693</v>
+        <v>0.4803149606299212</v>
       </c>
       <c r="L24">
-        <v>0.291044776119403</v>
+        <v>0.3090024330900243</v>
       </c>
       <c r="M24">
-        <v>390000</v>
+        <v>635000</v>
       </c>
       <c r="N24">
-        <v>300000</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="25" spans="9:14">
@@ -3782,16 +3782,16 @@
         <v>16</v>
       </c>
       <c r="K25">
-        <v>0.7529411764705882</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="L25">
-        <v>0.3102189781021898</v>
+        <v>0.2907801418439716</v>
       </c>
       <c r="M25">
-        <v>425000</v>
+        <v>615000</v>
       </c>
       <c r="N25">
-        <v>320000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="26" spans="9:14">
@@ -3802,16 +3802,16 @@
         <v>17</v>
       </c>
       <c r="K26">
-        <v>0.72</v>
+        <v>0.5508474576271186</v>
       </c>
       <c r="L26">
-        <v>0.3236245954692556</v>
+        <v>0.2616407982261641</v>
       </c>
       <c r="M26">
-        <v>500000</v>
+        <v>590000</v>
       </c>
       <c r="N26">
-        <v>360000</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="27" spans="9:14">
@@ -3822,13 +3822,13 @@
         <v>18</v>
       </c>
       <c r="K27">
-        <v>0.6404494382022472</v>
+        <v>0.504424778761062</v>
       </c>
       <c r="L27">
-        <v>0.3006756756756757</v>
+        <v>0.2621809744779582</v>
       </c>
       <c r="M27">
-        <v>445000</v>
+        <v>565000</v>
       </c>
       <c r="N27">
         <v>285000</v>
@@ -3842,16 +3842,16 @@
         <v>19</v>
       </c>
       <c r="K28">
-        <v>0.7192982456140351</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="L28">
-        <v>0.3689320388349515</v>
+        <v>0.3019693654266958</v>
       </c>
       <c r="M28">
-        <v>570000</v>
+        <v>690000</v>
       </c>
       <c r="N28">
-        <v>410000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="29" spans="9:14">
@@ -3862,16 +3862,16 @@
         <v>20</v>
       </c>
       <c r="K29">
-        <v>0.635593220338983</v>
+        <v>0.524822695035461</v>
       </c>
       <c r="L29">
-        <v>0.3856209150326798</v>
+        <v>0.3058568329718004</v>
       </c>
       <c r="M29">
-        <v>590000</v>
+        <v>705000</v>
       </c>
       <c r="N29">
-        <v>375000</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="30" spans="9:14">
@@ -3882,16 +3882,16 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>0.04285714285714286</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>0.2564102564102564</v>
+        <v>0.1472081218274112</v>
       </c>
       <c r="M30">
-        <v>350000</v>
+        <v>290000</v>
       </c>
       <c r="N30">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="9:14">
@@ -3902,16 +3902,16 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>0.1022727272727273</v>
+        <v>0.08139534883720931</v>
       </c>
       <c r="L31">
-        <v>0.2838709677419355</v>
+        <v>0.1950113378684807</v>
       </c>
       <c r="M31">
-        <v>440000</v>
+        <v>430000</v>
       </c>
       <c r="N31">
-        <v>45000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="32" spans="9:14">
@@ -3922,16 +3922,16 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>0.07954545454545454</v>
+        <v>0.1</v>
       </c>
       <c r="L32">
-        <v>0.3247232472324723</v>
+        <v>0.2546296296296297</v>
       </c>
       <c r="M32">
-        <v>440000</v>
+        <v>550000</v>
       </c>
       <c r="N32">
-        <v>35000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="33" spans="9:14">
@@ -3942,16 +3942,16 @@
         <v>11</v>
       </c>
       <c r="K33">
-        <v>0.07920792079207921</v>
+        <v>0.1319444444444444</v>
       </c>
       <c r="L33">
-        <v>0.3435374149659864</v>
+        <v>0.3150984682713348</v>
       </c>
       <c r="M33">
-        <v>505000</v>
+        <v>720000</v>
       </c>
       <c r="N33">
-        <v>40000</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="34" spans="9:14">
@@ -3962,16 +3962,16 @@
         <v>12</v>
       </c>
       <c r="K34">
-        <v>0.1</v>
+        <v>0.1060606060606061</v>
       </c>
       <c r="L34">
-        <v>0.3092783505154639</v>
+        <v>0.3</v>
       </c>
       <c r="M34">
-        <v>450000</v>
+        <v>660000</v>
       </c>
       <c r="N34">
-        <v>45000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="35" spans="9:14">
@@ -3982,16 +3982,16 @@
         <v>13</v>
       </c>
       <c r="K35">
-        <v>0.1739130434782609</v>
+        <v>0.1384615384615385</v>
       </c>
       <c r="L35">
-        <v>0.3565891472868217</v>
+        <v>0.3194103194103194</v>
       </c>
       <c r="M35">
-        <v>460000</v>
+        <v>650000</v>
       </c>
       <c r="N35">
-        <v>80000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="36" spans="9:14">
@@ -4002,16 +4002,16 @@
         <v>14</v>
       </c>
       <c r="K36">
-        <v>0.0379746835443038</v>
+        <v>0.1438356164383562</v>
       </c>
       <c r="L36">
-        <v>0.2705479452054795</v>
+        <v>0.3325740318906606</v>
       </c>
       <c r="M36">
-        <v>395000</v>
+        <v>730000</v>
       </c>
       <c r="N36">
-        <v>15000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="37" spans="9:14">
@@ -4022,16 +4022,16 @@
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.07526881720430108</v>
+        <v>0.1073825503355705</v>
       </c>
       <c r="L37">
-        <v>0.3470149253731343</v>
+        <v>0.3625304136253041</v>
       </c>
       <c r="M37">
-        <v>465000</v>
+        <v>745000</v>
       </c>
       <c r="N37">
-        <v>35000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="38" spans="9:14">
@@ -4042,16 +4042,16 @@
         <v>16</v>
       </c>
       <c r="K38">
-        <v>0.05</v>
+        <v>0.09467455621301775</v>
       </c>
       <c r="L38">
-        <v>0.364963503649635</v>
+        <v>0.3995271867612293</v>
       </c>
       <c r="M38">
-        <v>500000</v>
+        <v>845000</v>
       </c>
       <c r="N38">
-        <v>25000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="39" spans="9:14">
@@ -4062,16 +4062,16 @@
         <v>17</v>
       </c>
       <c r="K39">
-        <v>0.1071428571428571</v>
+        <v>0.096045197740113</v>
       </c>
       <c r="L39">
-        <v>0.3624595469255664</v>
+        <v>0.3924611973392461</v>
       </c>
       <c r="M39">
-        <v>560000</v>
+        <v>885000</v>
       </c>
       <c r="N39">
-        <v>60000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="40" spans="9:14">
@@ -4082,16 +4082,16 @@
         <v>18</v>
       </c>
       <c r="K40">
-        <v>0.1025641025641026</v>
+        <v>0.1058201058201058</v>
       </c>
       <c r="L40">
-        <v>0.3952702702702703</v>
+        <v>0.4385150812064965</v>
       </c>
       <c r="M40">
-        <v>585000</v>
+        <v>945000</v>
       </c>
       <c r="N40">
-        <v>60000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="41" spans="9:14">
@@ -4102,16 +4102,16 @@
         <v>19</v>
       </c>
       <c r="K41">
-        <v>0.07407407407407407</v>
+        <v>0.1182795698924731</v>
       </c>
       <c r="L41">
-        <v>0.3495145631067961</v>
+        <v>0.4070021881838075</v>
       </c>
       <c r="M41">
-        <v>540000</v>
+        <v>930000</v>
       </c>
       <c r="N41">
-        <v>40000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="42" spans="9:14">
@@ -4122,16 +4122,16 @@
         <v>20</v>
       </c>
       <c r="K42">
-        <v>0.04464285714285714</v>
+        <v>0.07804878048780488</v>
       </c>
       <c r="L42">
-        <v>0.3660130718954248</v>
+        <v>0.4446854663774403</v>
       </c>
       <c r="M42">
-        <v>560000</v>
+        <v>1025000</v>
       </c>
       <c r="N42">
-        <v>25000</v>
+        <v>80000</v>
       </c>
     </row>
   </sheetData>
